--- a/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_29.xlsx
+++ b/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H151"/>
+  <dimension ref="A1:M152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,4505 +469,6825 @@
           <t>Sensor_Status</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>CPU_Load_%</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Memory_Used_%</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Latency_ms</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Enc_Time_us</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Dec_Time_ms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:58.085</t>
+          <t>2026-05-29 09:49:10.413</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1779509333491</v>
+        <v>1780022949183</v>
       </c>
       <c r="C2" t="n">
-        <v>87329</v>
+        <v>75362</v>
       </c>
       <c r="D2" t="n">
-        <v>-242.63</v>
+        <v>-2586.97</v>
       </c>
       <c r="E2" t="n">
         <v>80</v>
       </c>
       <c r="F2" t="n">
-        <v>907</v>
+        <v>1099</v>
       </c>
       <c r="G2" t="n">
-        <v>141.83</v>
+        <v>291.49</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I2" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J2" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1229</v>
+      </c>
+      <c r="L2" t="n">
+        <v>115</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.988</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:58.086</t>
+          <t>2026-05-29 09:49:10.415</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1779509333693</v>
+        <v>1780022949383</v>
       </c>
       <c r="C3" t="n">
-        <v>87412</v>
+        <v>75333</v>
       </c>
       <c r="D3" t="n">
-        <v>-147.5</v>
+        <v>-2486.62</v>
       </c>
       <c r="E3" t="n">
         <v>80</v>
       </c>
       <c r="F3" t="n">
-        <v>907</v>
+        <v>1099</v>
       </c>
       <c r="G3" t="n">
-        <v>141.83</v>
+        <v>291.49</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I3" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J3" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L3" t="n">
+        <v>116</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.852</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:58.442</t>
+          <t>2026-05-29 09:49:10.609</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1779509333894</v>
+        <v>1780022949602</v>
       </c>
       <c r="C4" t="n">
-        <v>87590</v>
+        <v>75439</v>
       </c>
       <c r="D4" t="n">
-        <v>37.87</v>
+        <v>-2256.29</v>
       </c>
       <c r="E4" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F4" t="n">
-        <v>644</v>
+        <v>1099</v>
       </c>
       <c r="G4" t="n">
-        <v>140.61</v>
+        <v>291.49</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I4" t="n">
+        <v>49.26</v>
+      </c>
+      <c r="J4" t="n">
+        <v>34.51</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1006</v>
+      </c>
+      <c r="L4" t="n">
+        <v>117</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.189</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:58.457</t>
+          <t>2026-05-29 09:49:10.619</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1779509334095</v>
+        <v>1780022949802</v>
       </c>
       <c r="C5" t="n">
-        <v>87166</v>
+        <v>75254</v>
       </c>
       <c r="D5" t="n">
-        <v>-388.02</v>
+        <v>-2328.48</v>
       </c>
       <c r="E5" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F5" t="n">
-        <v>644</v>
+        <v>1099</v>
       </c>
       <c r="G5" t="n">
-        <v>140.61</v>
+        <v>291.49</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I5" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J5" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="K5" t="n">
+        <v>816</v>
+      </c>
+      <c r="L5" t="n">
+        <v>110</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.671</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:59.088</t>
+          <t>2026-05-29 09:49:11.165</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1779509334297</v>
+        <v>1780022950002</v>
       </c>
       <c r="C6" t="n">
-        <v>87242</v>
+        <v>75266</v>
       </c>
       <c r="D6" t="n">
-        <v>-292.62</v>
+        <v>-2200.05</v>
       </c>
       <c r="E6" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F6" t="n">
-        <v>644</v>
+        <v>1099</v>
       </c>
       <c r="G6" t="n">
-        <v>140.61</v>
+        <v>291.49</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I6" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J6" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1162</v>
+      </c>
+      <c r="L6" t="n">
+        <v>113</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.054</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:59.091</t>
+          <t>2026-05-29 09:49:11.166</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1779509334498</v>
+        <v>1780022950202</v>
       </c>
       <c r="C7" t="n">
-        <v>87505</v>
+        <v>75363</v>
       </c>
       <c r="D7" t="n">
-        <v>-14.99</v>
+        <v>-1993.05</v>
       </c>
       <c r="E7" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F7" t="n">
-        <v>644</v>
+        <v>1099</v>
       </c>
       <c r="G7" t="n">
-        <v>140.61</v>
+        <v>291.49</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I7" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J7" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="K7" t="n">
+        <v>963</v>
+      </c>
+      <c r="L7" t="n">
+        <v>109</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.518</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:59.134</t>
+          <t>2026-05-29 09:49:11.465</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1779509334700</v>
+        <v>1780022950402</v>
       </c>
       <c r="C8" t="n">
-        <v>87232</v>
+        <v>75097</v>
       </c>
       <c r="D8" t="n">
-        <v>-287.24</v>
+        <v>-2159.4</v>
       </c>
       <c r="E8" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F8" t="n">
-        <v>685</v>
+        <v>3938</v>
       </c>
       <c r="G8" t="n">
-        <v>134.3</v>
+        <v>291.49</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I8" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J8" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1061</v>
+      </c>
+      <c r="L8" t="n">
+        <v>108</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.355</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:59.135</t>
+          <t>2026-05-29 09:49:11.466</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1779509334901</v>
+        <v>1780022950602</v>
       </c>
       <c r="C9" t="n">
-        <v>87303</v>
+        <v>75103</v>
       </c>
       <c r="D9" t="n">
-        <v>-201.88</v>
+        <v>-2045.43</v>
       </c>
       <c r="E9" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F9" t="n">
-        <v>685</v>
+        <v>3938</v>
       </c>
       <c r="G9" t="n">
-        <v>134.3</v>
+        <v>291.49</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I9" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J9" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="K9" t="n">
+        <v>863</v>
+      </c>
+      <c r="L9" t="n">
+        <v>110</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.245</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:59.545</t>
+          <t>2026-05-29 09:49:11.957</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1779509335102</v>
+        <v>1780022950802</v>
       </c>
       <c r="C10" t="n">
-        <v>87555</v>
+        <v>75142</v>
       </c>
       <c r="D10" t="n">
-        <v>60.22</v>
+        <v>-1904.16</v>
       </c>
       <c r="E10" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F10" t="n">
-        <v>685</v>
+        <v>3938</v>
       </c>
       <c r="G10" t="n">
-        <v>134.3</v>
+        <v>291.49</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I10" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J10" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1154</v>
+      </c>
+      <c r="L10" t="n">
+        <v>111</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.799</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:59.842</t>
+          <t>2026-05-29 09:49:11.973</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1779509335304</v>
+        <v>1780022951002</v>
       </c>
       <c r="C11" t="n">
-        <v>87760</v>
+        <v>74923</v>
       </c>
       <c r="D11" t="n">
-        <v>262.21</v>
+        <v>-2027.95</v>
       </c>
       <c r="E11" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="F11" t="n">
-        <v>583</v>
+        <v>3938</v>
       </c>
       <c r="G11" t="n">
-        <v>140.88</v>
+        <v>291.49</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I11" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J11" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="K11" t="n">
+        <v>970</v>
+      </c>
+      <c r="L11" t="n">
+        <v>106</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.988</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:59.843</t>
+          <t>2026-05-29 09:49:12.269</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1779509335505</v>
+        <v>1780022951202</v>
       </c>
       <c r="C12" t="n">
-        <v>87302</v>
+        <v>75269</v>
       </c>
       <c r="D12" t="n">
-        <v>-208.9</v>
+        <v>-1580.55</v>
       </c>
       <c r="E12" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="F12" t="n">
-        <v>583</v>
+        <v>3938</v>
       </c>
       <c r="G12" t="n">
-        <v>140.88</v>
+        <v>291.49</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I12" t="n">
+        <v>49.48</v>
+      </c>
+      <c r="J12" t="n">
+        <v>35.02</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1066</v>
+      </c>
+      <c r="L12" t="n">
+        <v>109</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.669</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:00.114</t>
+          <t>2026-05-29 09:49:12.271</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1779509335706</v>
+        <v>1780022951421</v>
       </c>
       <c r="C13" t="n">
-        <v>87494</v>
+        <v>75090</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.46</v>
+        <v>-1680.52</v>
       </c>
       <c r="E13" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="F13" t="n">
-        <v>583</v>
+        <v>1060</v>
       </c>
       <c r="G13" t="n">
-        <v>140.88</v>
+        <v>287.9</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I13" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J13" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="K13" t="n">
+        <v>849</v>
+      </c>
+      <c r="L13" t="n">
+        <v>112</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.018</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:00.118</t>
+          <t>2026-05-29 09:49:12.842</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1779509335908</v>
+        <v>1780022951621</v>
       </c>
       <c r="C14" t="n">
-        <v>87744</v>
+        <v>74921</v>
       </c>
       <c r="D14" t="n">
-        <v>243.86</v>
+        <v>-1765.5</v>
       </c>
       <c r="E14" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="F14" t="n">
-        <v>583</v>
+        <v>1060</v>
       </c>
       <c r="G14" t="n">
-        <v>140.88</v>
+        <v>287.9</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I14" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J14" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1219</v>
+      </c>
+      <c r="L14" t="n">
+        <v>112</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.144</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:00.426</t>
+          <t>2026-05-29 09:49:12.858</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1779509336109</v>
+        <v>1780022951821</v>
       </c>
       <c r="C15" t="n">
-        <v>87899</v>
+        <v>75052</v>
       </c>
       <c r="D15" t="n">
-        <v>386.67</v>
+        <v>-1546.22</v>
       </c>
       <c r="E15" t="n">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="F15" t="n">
-        <v>786</v>
+        <v>1060</v>
       </c>
       <c r="G15" t="n">
-        <v>123.17</v>
+        <v>287.9</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I15" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J15" t="n">
+        <v>35.02</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1035</v>
+      </c>
+      <c r="L15" t="n">
+        <v>108</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.052</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:00.439</t>
+          <t>2026-05-29 09:49:12.860</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1779509336310</v>
+        <v>1780022952021</v>
       </c>
       <c r="C16" t="n">
-        <v>87482</v>
+        <v>75203</v>
       </c>
       <c r="D16" t="n">
-        <v>-49.66</v>
+        <v>-1317.91</v>
       </c>
       <c r="E16" t="n">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="F16" t="n">
-        <v>786</v>
+        <v>1060</v>
       </c>
       <c r="G16" t="n">
-        <v>123.17</v>
+        <v>287.9</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I16" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>35.02</v>
+      </c>
+      <c r="K16" t="n">
+        <v>838</v>
+      </c>
+      <c r="L16" t="n">
+        <v>99</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:01.231</t>
+          <t>2026-05-29 09:49:13.327</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1779509336512</v>
+        <v>1780022952221</v>
       </c>
       <c r="C17" t="n">
-        <v>87640</v>
+        <v>75177</v>
       </c>
       <c r="D17" t="n">
-        <v>110.82</v>
+        <v>-1278.02</v>
       </c>
       <c r="E17" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="F17" t="n">
-        <v>786</v>
+        <v>719</v>
       </c>
       <c r="G17" t="n">
-        <v>123.17</v>
+        <v>267.03</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I17" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J17" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1105</v>
+      </c>
+      <c r="L17" t="n">
+        <v>106</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.132</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:01.505</t>
+          <t>2026-05-29 09:49:13.340</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1779509336713</v>
+        <v>1780022952421</v>
       </c>
       <c r="C18" t="n">
-        <v>87843</v>
+        <v>75119</v>
       </c>
       <c r="D18" t="n">
-        <v>308.28</v>
+        <v>-1272.12</v>
       </c>
       <c r="E18" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="F18" t="n">
-        <v>765</v>
+        <v>719</v>
       </c>
       <c r="G18" t="n">
-        <v>93.53</v>
+        <v>267.03</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I18" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J18" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="K18" t="n">
+        <v>917</v>
+      </c>
+      <c r="L18" t="n">
+        <v>105</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.434</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:01.507</t>
+          <t>2026-05-29 09:49:14.474</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1779509336915</v>
+        <v>1780022952621</v>
       </c>
       <c r="C19" t="n">
-        <v>87816</v>
+        <v>75237</v>
       </c>
       <c r="D19" t="n">
-        <v>265.87</v>
+        <v>-1090.51</v>
       </c>
       <c r="E19" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="F19" t="n">
-        <v>765</v>
+        <v>719</v>
       </c>
       <c r="G19" t="n">
-        <v>93.53</v>
+        <v>267.03</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I19" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J19" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1853</v>
+      </c>
+      <c r="L19" t="n">
+        <v>106</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.744</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:01.553</t>
+          <t>2026-05-29 09:49:14.476</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1779509337116</v>
+        <v>1780022952821</v>
       </c>
       <c r="C20" t="n">
-        <v>87587</v>
+        <v>75301</v>
       </c>
       <c r="D20" t="n">
-        <v>23.57</v>
+        <v>-971.98</v>
       </c>
       <c r="E20" t="n">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="F20" t="n">
-        <v>765</v>
+        <v>600</v>
       </c>
       <c r="G20" t="n">
-        <v>93.53</v>
+        <v>276.8</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I20" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J20" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1654</v>
+      </c>
+      <c r="L20" t="n">
+        <v>109</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.225</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:01.848</t>
+          <t>2026-05-29 09:49:14.478</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1779509337317</v>
+        <v>1780022953021</v>
       </c>
       <c r="C21" t="n">
-        <v>87819</v>
+        <v>75128</v>
       </c>
       <c r="D21" t="n">
-        <v>254.39</v>
+        <v>-1096.39</v>
       </c>
       <c r="E21" t="n">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="F21" t="n">
-        <v>765</v>
+        <v>600</v>
       </c>
       <c r="G21" t="n">
-        <v>93.53</v>
+        <v>276.8</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I21" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J21" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1456</v>
+      </c>
+      <c r="L21" t="n">
+        <v>109</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.307</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:01.849</t>
+          <t>2026-05-29 09:49:14.479</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1779509337519</v>
+        <v>1780022953221</v>
       </c>
       <c r="C22" t="n">
-        <v>88021</v>
+        <v>75202</v>
       </c>
       <c r="D22" t="n">
-        <v>443.67</v>
+        <v>-967.5700000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="F22" t="n">
-        <v>745</v>
+        <v>600</v>
       </c>
       <c r="G22" t="n">
-        <v>90.68000000000001</v>
+        <v>276.8</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I22" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J22" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1257</v>
+      </c>
+      <c r="L22" t="n">
+        <v>107</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.051</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:01.849</t>
+          <t>2026-05-29 09:49:14.491</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1779509337720</v>
+        <v>1780022953440</v>
       </c>
       <c r="C23" t="n">
-        <v>87597</v>
+        <v>75375</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.51</v>
+        <v>-746.1900000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F23" t="n">
-        <v>745</v>
+        <v>659</v>
       </c>
       <c r="G23" t="n">
-        <v>90.68000000000001</v>
+        <v>193.22</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I23" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J23" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1049</v>
+      </c>
+      <c r="L23" t="n">
+        <v>107</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.361</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:02.116</t>
+          <t>2026-05-29 09:49:14.720</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1779509337921</v>
+        <v>1780022953640</v>
       </c>
       <c r="C24" t="n">
-        <v>87646</v>
+        <v>75022</v>
       </c>
       <c r="D24" t="n">
-        <v>46.62</v>
+        <v>-1061.88</v>
       </c>
       <c r="E24" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F24" t="n">
-        <v>745</v>
+        <v>659</v>
       </c>
       <c r="G24" t="n">
-        <v>90.68000000000001</v>
+        <v>193.22</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I24" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J24" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1079</v>
+      </c>
+      <c r="L24" t="n">
+        <v>110</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.904</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:02.424</t>
+          <t>2026-05-29 09:49:14.736</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1779509338123</v>
+        <v>1780022953840</v>
       </c>
       <c r="C25" t="n">
-        <v>88020</v>
+        <v>75224</v>
       </c>
       <c r="D25" t="n">
-        <v>418.29</v>
+        <v>-806.78</v>
       </c>
       <c r="E25" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F25" t="n">
-        <v>745</v>
+        <v>659</v>
       </c>
       <c r="G25" t="n">
-        <v>90.68000000000001</v>
+        <v>193.22</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I25" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J25" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K25" t="n">
+        <v>895</v>
+      </c>
+      <c r="L25" t="n">
+        <v>111</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.755</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:02.712</t>
+          <t>2026-05-29 09:49:15.149</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1779509338324</v>
+        <v>1780022954040</v>
       </c>
       <c r="C26" t="n">
-        <v>87625</v>
+        <v>75385</v>
       </c>
       <c r="D26" t="n">
-        <v>2.37</v>
+        <v>-605.45</v>
       </c>
       <c r="E26" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="F26" t="n">
-        <v>725</v>
+        <v>640</v>
       </c>
       <c r="G26" t="n">
-        <v>88.38</v>
+        <v>188.57</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I26" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J26" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1108</v>
+      </c>
+      <c r="L26" t="n">
+        <v>106</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.06</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:02.749</t>
+          <t>2026-05-29 09:49:15.201</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1779509338525</v>
+        <v>1780022954240</v>
       </c>
       <c r="C27" t="n">
-        <v>87757</v>
+        <v>75003</v>
       </c>
       <c r="D27" t="n">
-        <v>134.25</v>
+        <v>-957.17</v>
       </c>
       <c r="E27" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="F27" t="n">
-        <v>725</v>
+        <v>640</v>
       </c>
       <c r="G27" t="n">
-        <v>88.38</v>
+        <v>188.57</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I27" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J27" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K27" t="n">
+        <v>959</v>
+      </c>
+      <c r="L27" t="n">
+        <v>104</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2.141</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:03.037</t>
+          <t>2026-05-29 09:49:15.769</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1779509338727</v>
+        <v>1780022954440</v>
       </c>
       <c r="C28" t="n">
-        <v>87913</v>
+        <v>75098</v>
       </c>
       <c r="D28" t="n">
-        <v>283.54</v>
+        <v>-814.3099999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="F28" t="n">
-        <v>725</v>
+        <v>640</v>
       </c>
       <c r="G28" t="n">
-        <v>88.38</v>
+        <v>188.57</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I28" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J28" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1328</v>
+      </c>
+      <c r="L28" t="n">
+        <v>120</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.003</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:03.318</t>
+          <t>2026-05-29 09:49:15.771</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1779509338928</v>
+        <v>1780022954640</v>
       </c>
       <c r="C29" t="n">
-        <v>88060</v>
+        <v>75219</v>
       </c>
       <c r="D29" t="n">
-        <v>416.36</v>
+        <v>-652.6</v>
       </c>
       <c r="E29" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F29" t="n">
-        <v>604</v>
+        <v>640</v>
       </c>
       <c r="G29" t="n">
-        <v>95.45</v>
+        <v>188.57</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I29" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J29" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1130</v>
+      </c>
+      <c r="L29" t="n">
+        <v>107</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.097</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:03.320</t>
+          <t>2026-05-29 09:49:15.773</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1779509339130</v>
+        <v>1780022954840</v>
       </c>
       <c r="C30" t="n">
-        <v>87799</v>
+        <v>74923</v>
       </c>
       <c r="D30" t="n">
-        <v>134.54</v>
+        <v>-915.97</v>
       </c>
       <c r="E30" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F30" t="n">
-        <v>604</v>
+        <v>800</v>
       </c>
       <c r="G30" t="n">
-        <v>95.45</v>
+        <v>182.15</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I30" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J30" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K30" t="n">
+        <v>931</v>
+      </c>
+      <c r="L30" t="n">
+        <v>105</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.251</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:03.717</t>
+          <t>2026-05-29 09:49:16.133</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1779509339331</v>
+        <v>1780022955040</v>
       </c>
       <c r="C31" t="n">
-        <v>87941</v>
+        <v>75096</v>
       </c>
       <c r="D31" t="n">
-        <v>269.82</v>
+        <v>-697.17</v>
       </c>
       <c r="E31" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F31" t="n">
-        <v>604</v>
+        <v>800</v>
       </c>
       <c r="G31" t="n">
-        <v>95.45</v>
+        <v>182.15</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I31" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J31" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1092</v>
+      </c>
+      <c r="L31" t="n">
+        <v>107</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.161</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:03.735</t>
+          <t>2026-05-29 09:49:16.135</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1779509339532</v>
+        <v>1780022955259</v>
       </c>
       <c r="C32" t="n">
-        <v>88016</v>
+        <v>75197</v>
       </c>
       <c r="D32" t="n">
-        <v>331.33</v>
+        <v>-561.3099999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F32" t="n">
-        <v>725</v>
+        <v>800</v>
       </c>
       <c r="G32" t="n">
-        <v>94.95999999999999</v>
+        <v>182.15</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I32" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J32" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K32" t="n">
+        <v>875</v>
+      </c>
+      <c r="L32" t="n">
+        <v>107</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.313</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:03.933</t>
+          <t>2026-05-29 09:49:16.536</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1779509339734</v>
+        <v>1780022955459</v>
       </c>
       <c r="C33" t="n">
-        <v>87657</v>
+        <v>75227</v>
       </c>
       <c r="D33" t="n">
-        <v>-44.24</v>
+        <v>-503.25</v>
       </c>
       <c r="E33" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F33" t="n">
-        <v>725</v>
+        <v>519</v>
       </c>
       <c r="G33" t="n">
-        <v>94.95999999999999</v>
+        <v>197.01</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I33" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J33" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1075</v>
+      </c>
+      <c r="L33" t="n">
+        <v>109</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.41</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:03.935</t>
+          <t>2026-05-29 09:49:16.537</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1779509339935</v>
+        <v>1780022955659</v>
       </c>
       <c r="C34" t="n">
-        <v>87891</v>
+        <v>75242</v>
       </c>
       <c r="D34" t="n">
-        <v>191.97</v>
+        <v>-463.08</v>
       </c>
       <c r="E34" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F34" t="n">
-        <v>725</v>
+        <v>519</v>
       </c>
       <c r="G34" t="n">
-        <v>94.95999999999999</v>
+        <v>197.01</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I34" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J34" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K34" t="n">
+        <v>877</v>
+      </c>
+      <c r="L34" t="n">
+        <v>104</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.396</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:04.242</t>
+          <t>2026-05-29 09:49:17.059</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1779509340136</v>
+        <v>1780022955859</v>
       </c>
       <c r="C35" t="n">
-        <v>88091</v>
+        <v>75334</v>
       </c>
       <c r="D35" t="n">
-        <v>382.37</v>
+        <v>-347.93</v>
       </c>
       <c r="E35" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F35" t="n">
-        <v>624</v>
+        <v>519</v>
       </c>
       <c r="G35" t="n">
-        <v>71.20999999999999</v>
+        <v>197.01</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I35" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J35" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1198</v>
+      </c>
+      <c r="L35" t="n">
+        <v>108</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.461</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:04.528</t>
+          <t>2026-05-29 09:49:17.074</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1779509340338</v>
+        <v>1780022956059</v>
       </c>
       <c r="C36" t="n">
-        <v>87651</v>
+        <v>75329</v>
       </c>
       <c r="D36" t="n">
-        <v>-76.75</v>
+        <v>-335.53</v>
       </c>
       <c r="E36" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F36" t="n">
-        <v>624</v>
+        <v>519</v>
       </c>
       <c r="G36" t="n">
-        <v>71.20999999999999</v>
+        <v>197.01</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I36" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J36" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1014</v>
+      </c>
+      <c r="L36" t="n">
+        <v>106</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.123</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:04.818</t>
+          <t>2026-05-29 09:49:17.130</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1779509340539</v>
+        <v>1780022956259</v>
       </c>
       <c r="C37" t="n">
-        <v>87807</v>
+        <v>75101</v>
       </c>
       <c r="D37" t="n">
-        <v>83.09</v>
+        <v>-546.76</v>
       </c>
       <c r="E37" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F37" t="n">
-        <v>624</v>
+        <v>519</v>
       </c>
       <c r="G37" t="n">
-        <v>71.20999999999999</v>
+        <v>197.01</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I37" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J37" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="K37" t="n">
+        <v>870</v>
+      </c>
+      <c r="L37" t="n">
+        <v>101</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.426</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:04.819</t>
+          <t>2026-05-29 09:49:17.417</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1779509340740</v>
+        <v>1780022956459</v>
       </c>
       <c r="C38" t="n">
-        <v>87945</v>
+        <v>75173</v>
       </c>
       <c r="D38" t="n">
-        <v>216.94</v>
+        <v>-447.42</v>
       </c>
       <c r="E38" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F38" t="n">
-        <v>624</v>
+        <v>519</v>
       </c>
       <c r="G38" t="n">
-        <v>71.20999999999999</v>
+        <v>197.01</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I38" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J38" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K38" t="n">
+        <v>957</v>
+      </c>
+      <c r="L38" t="n">
+        <v>108</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.9379999999999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:05.203</t>
+          <t>2026-05-29 09:49:17.811</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1779509340942</v>
+        <v>1780022956659</v>
       </c>
       <c r="C39" t="n">
-        <v>88072</v>
+        <v>75445</v>
       </c>
       <c r="D39" t="n">
-        <v>333.09</v>
+        <v>-153.05</v>
       </c>
       <c r="E39" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="F39" t="n">
-        <v>725</v>
+        <v>1360</v>
       </c>
       <c r="G39" t="n">
-        <v>70.17</v>
+        <v>269.6</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I39" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J39" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1150</v>
+      </c>
+      <c r="L39" t="n">
+        <v>119</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.485</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:05.483</t>
+          <t>2026-05-29 09:49:17.873</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1779509341143</v>
+        <v>1780022956878</v>
       </c>
       <c r="C40" t="n">
-        <v>87584</v>
+        <v>75767</v>
       </c>
       <c r="D40" t="n">
-        <v>-171.56</v>
+        <v>176.6</v>
       </c>
       <c r="E40" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="F40" t="n">
-        <v>725</v>
+        <v>1360</v>
       </c>
       <c r="G40" t="n">
-        <v>70.17</v>
+        <v>269.6</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I40" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J40" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K40" t="n">
+        <v>994</v>
+      </c>
+      <c r="L40" t="n">
+        <v>117</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.404</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:05.784</t>
+          <t>2026-05-29 09:49:18.181</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1779509341344</v>
+        <v>1780022957078</v>
       </c>
       <c r="C41" t="n">
-        <v>87942</v>
+        <v>76393</v>
       </c>
       <c r="D41" t="n">
-        <v>195.01</v>
+        <v>793.77</v>
       </c>
       <c r="E41" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="F41" t="n">
-        <v>725</v>
+        <v>1360</v>
       </c>
       <c r="G41" t="n">
-        <v>70.17</v>
+        <v>269.6</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I41" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J41" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1102</v>
+      </c>
+      <c r="L41" t="n">
+        <v>110</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.767</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:06.057</t>
+          <t>2026-05-29 09:49:18.182</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1779509341546</v>
+        <v>1780022957278</v>
       </c>
       <c r="C42" t="n">
-        <v>88034</v>
+        <v>76308</v>
       </c>
       <c r="D42" t="n">
-        <v>277.26</v>
+        <v>669.09</v>
       </c>
       <c r="E42" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="F42" t="n">
-        <v>644</v>
+        <v>1360</v>
       </c>
       <c r="G42" t="n">
-        <v>72.09999999999999</v>
+        <v>269.6</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I42" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J42" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K42" t="n">
+        <v>903</v>
+      </c>
+      <c r="L42" t="n">
+        <v>109</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.573</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:06.058</t>
+          <t>2026-05-29 09:49:18.793</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1779509341747</v>
+        <v>1780022957478</v>
       </c>
       <c r="C43" t="n">
-        <v>87614</v>
+        <v>75965</v>
       </c>
       <c r="D43" t="n">
-        <v>-156.6</v>
+        <v>292.63</v>
       </c>
       <c r="E43" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="F43" t="n">
-        <v>644</v>
+        <v>1360</v>
       </c>
       <c r="G43" t="n">
-        <v>72.09999999999999</v>
+        <v>269.6</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I43" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J43" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1314</v>
+      </c>
+      <c r="L43" t="n">
+        <v>109</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.046</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:06.060</t>
+          <t>2026-05-29 09:49:18.802</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1779509341949</v>
+        <v>1780022957678</v>
       </c>
       <c r="C44" t="n">
-        <v>87809</v>
+        <v>76736</v>
       </c>
       <c r="D44" t="n">
-        <v>46.23</v>
+        <v>1049</v>
       </c>
       <c r="E44" t="n">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="F44" t="n">
-        <v>644</v>
+        <v>1019</v>
       </c>
       <c r="G44" t="n">
-        <v>72.09999999999999</v>
+        <v>272.23</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I44" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J44" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1123</v>
+      </c>
+      <c r="L44" t="n">
+        <v>113</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.895</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:06.313</t>
+          <t>2026-05-29 09:49:18.803</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1779509342150</v>
+        <v>1780022957878</v>
       </c>
       <c r="C45" t="n">
-        <v>88031</v>
+        <v>75656</v>
       </c>
       <c r="D45" t="n">
-        <v>265.92</v>
+        <v>-83.45</v>
       </c>
       <c r="E45" t="n">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="F45" t="n">
-        <v>644</v>
+        <v>1019</v>
       </c>
       <c r="G45" t="n">
-        <v>72.09999999999999</v>
+        <v>272.23</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I45" t="n">
+        <v>49.27</v>
+      </c>
+      <c r="J45" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K45" t="n">
+        <v>924</v>
+      </c>
+      <c r="L45" t="n">
+        <v>112</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.849</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:06.313</t>
+          <t>2026-05-29 09:49:19.220</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1779509342351</v>
+        <v>1780022958079</v>
       </c>
       <c r="C46" t="n">
-        <v>87871</v>
+        <v>75732</v>
       </c>
       <c r="D46" t="n">
-        <v>92.62</v>
+        <v>-3.28</v>
       </c>
       <c r="E46" t="n">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="F46" t="n">
-        <v>725</v>
+        <v>1019</v>
       </c>
       <c r="G46" t="n">
-        <v>61.29</v>
+        <v>272.23</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I46" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J46" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1140</v>
+      </c>
+      <c r="L46" t="n">
+        <v>106</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.209</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:06.597</t>
+          <t>2026-05-29 09:49:19.222</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1779509342553</v>
+        <v>1780022958278</v>
       </c>
       <c r="C47" t="n">
-        <v>87640</v>
+        <v>75429</v>
       </c>
       <c r="D47" t="n">
-        <v>-143.01</v>
+        <v>-306.11</v>
       </c>
       <c r="E47" t="n">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="F47" t="n">
-        <v>725</v>
+        <v>1019</v>
       </c>
       <c r="G47" t="n">
-        <v>61.29</v>
+        <v>272.23</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I47" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J47" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K47" t="n">
+        <v>942</v>
+      </c>
+      <c r="L47" t="n">
+        <v>116</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.018</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:06.867</t>
+          <t>2026-05-29 09:49:19.627</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1779509342754</v>
+        <v>1780022958479</v>
       </c>
       <c r="C48" t="n">
-        <v>87842</v>
+        <v>75960</v>
       </c>
       <c r="D48" t="n">
-        <v>66.14</v>
+        <v>240.19</v>
       </c>
       <c r="E48" t="n">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="F48" t="n">
-        <v>725</v>
+        <v>1019</v>
       </c>
       <c r="G48" t="n">
-        <v>61.29</v>
+        <v>272.23</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I48" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="J48" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1147</v>
+      </c>
+      <c r="L48" t="n">
+        <v>108</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1.041</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:07.448</t>
+          <t>2026-05-29 09:49:19.680</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1779509342955</v>
+        <v>1780022958697</v>
       </c>
       <c r="C49" t="n">
-        <v>87998</v>
+        <v>75675</v>
       </c>
       <c r="D49" t="n">
-        <v>218.84</v>
+        <v>-56.82</v>
       </c>
       <c r="E49" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="F49" t="n">
-        <v>705</v>
+        <v>939</v>
       </c>
       <c r="G49" t="n">
-        <v>54.66</v>
+        <v>260.25</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I49" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J49" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K49" t="n">
+        <v>982</v>
+      </c>
+      <c r="L49" t="n">
+        <v>107</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1.239</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:07.688</t>
+          <t>2026-05-29 09:49:20.037</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1779509343157</v>
+        <v>1780022958897</v>
       </c>
       <c r="C50" t="n">
-        <v>87556</v>
+        <v>77537</v>
       </c>
       <c r="D50" t="n">
-        <v>-234.11</v>
+        <v>1808.02</v>
       </c>
       <c r="E50" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="F50" t="n">
-        <v>705</v>
+        <v>939</v>
       </c>
       <c r="G50" t="n">
-        <v>54.66</v>
+        <v>260.25</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I50" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="J50" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1139</v>
+      </c>
+      <c r="L50" t="n">
+        <v>114</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.196</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:07.691</t>
+          <t>2026-05-29 09:49:20.068</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1779509343358</v>
+        <v>1780022959097</v>
       </c>
       <c r="C51" t="n">
-        <v>87755</v>
+        <v>77314</v>
       </c>
       <c r="D51" t="n">
-        <v>-23.4</v>
+        <v>1494.62</v>
       </c>
       <c r="E51" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="F51" t="n">
-        <v>705</v>
+        <v>939</v>
       </c>
       <c r="G51" t="n">
-        <v>54.66</v>
+        <v>260.25</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I51" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J51" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K51" t="n">
+        <v>969</v>
+      </c>
+      <c r="L51" t="n">
+        <v>108</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1.511</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:07.759</t>
+          <t>2026-05-29 09:49:20.082</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1779509343559</v>
+        <v>1780022959297</v>
       </c>
       <c r="C52" t="n">
-        <v>88016</v>
+        <v>76540</v>
       </c>
       <c r="D52" t="n">
-        <v>238.77</v>
+        <v>645.89</v>
       </c>
       <c r="E52" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="F52" t="n">
-        <v>705</v>
+        <v>939</v>
       </c>
       <c r="G52" t="n">
-        <v>54.66</v>
+        <v>260.25</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I52" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J52" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="K52" t="n">
+        <v>784</v>
+      </c>
+      <c r="L52" t="n">
+        <v>112</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.898</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:08.137</t>
+          <t>2026-05-29 09:49:20.416</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1779509343761</v>
+        <v>1780022959497</v>
       </c>
       <c r="C53" t="n">
-        <v>87991</v>
+        <v>76816</v>
       </c>
       <c r="D53" t="n">
-        <v>201.83</v>
+        <v>889.6</v>
       </c>
       <c r="E53" t="n">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="F53" t="n">
-        <v>685</v>
+        <v>939</v>
       </c>
       <c r="G53" t="n">
-        <v>49.48</v>
+        <v>260.25</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I53" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J53" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K53" t="n">
+        <v>918</v>
+      </c>
+      <c r="L53" t="n">
+        <v>117</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1.032</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:08.395</t>
+          <t>2026-05-29 09:49:20.417</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1779509343962</v>
+        <v>1780022959698</v>
       </c>
       <c r="C54" t="n">
-        <v>87706</v>
+        <v>76721</v>
       </c>
       <c r="D54" t="n">
-        <v>-93.26000000000001</v>
+        <v>750.12</v>
       </c>
       <c r="E54" t="n">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="F54" t="n">
-        <v>685</v>
+        <v>939</v>
       </c>
       <c r="G54" t="n">
-        <v>49.48</v>
+        <v>260.25</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I54" t="n">
+        <v>50.08</v>
+      </c>
+      <c r="J54" t="n">
+        <v>35.06</v>
+      </c>
+      <c r="K54" t="n">
+        <v>719</v>
+      </c>
+      <c r="L54" t="n">
+        <v>107</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.518</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:08.396</t>
+          <t>2026-05-29 09:49:20.941</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1779509344164</v>
+        <v>1780022959917</v>
       </c>
       <c r="C55" t="n">
-        <v>87849</v>
+        <v>76145</v>
       </c>
       <c r="D55" t="n">
-        <v>54.4</v>
+        <v>136.61</v>
       </c>
       <c r="E55" t="n">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="F55" t="n">
-        <v>685</v>
+        <v>939</v>
       </c>
       <c r="G55" t="n">
-        <v>49.48</v>
+        <v>260.25</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I55" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J55" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1022</v>
+      </c>
+      <c r="L55" t="n">
+        <v>112</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1.271</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:08.649</t>
+          <t>2026-05-29 09:49:21.293</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1779509344365</v>
+        <v>1780022960117</v>
       </c>
       <c r="C56" t="n">
-        <v>87929</v>
+        <v>75553</v>
       </c>
       <c r="D56" t="n">
-        <v>131.68</v>
+        <v>-462.22</v>
       </c>
       <c r="E56" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="F56" t="n">
-        <v>765</v>
+        <v>939</v>
       </c>
       <c r="G56" t="n">
-        <v>52.25</v>
+        <v>260.25</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I56" t="n">
+        <v>49.47</v>
+      </c>
+      <c r="J56" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1176</v>
+      </c>
+      <c r="L56" t="n">
+        <v>123</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.515</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:08.651</t>
+          <t>2026-05-29 09:49:21.295</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1779509344566</v>
+        <v>1780022960336</v>
       </c>
       <c r="C57" t="n">
-        <v>87559</v>
+        <v>76916</v>
       </c>
       <c r="D57" t="n">
-        <v>-244.9</v>
+        <v>923.89</v>
       </c>
       <c r="E57" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="F57" t="n">
-        <v>765</v>
+        <v>939</v>
       </c>
       <c r="G57" t="n">
-        <v>52.25</v>
+        <v>260.25</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I57" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J57" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K57" t="n">
+        <v>957</v>
+      </c>
+      <c r="L57" t="n">
+        <v>107</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1.188</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:08.949</t>
+          <t>2026-05-29 09:49:21.641</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1779509344768</v>
+        <v>1780022960536</v>
       </c>
       <c r="C58" t="n">
-        <v>87668</v>
+        <v>75910</v>
       </c>
       <c r="D58" t="n">
-        <v>-123.66</v>
+        <v>-128.3</v>
       </c>
       <c r="E58" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="F58" t="n">
-        <v>765</v>
+        <v>939</v>
       </c>
       <c r="G58" t="n">
-        <v>52.25</v>
+        <v>260.25</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I58" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="J58" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1104</v>
+      </c>
+      <c r="L58" t="n">
+        <v>113</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.878</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:08.950</t>
+          <t>2026-05-29 09:49:21.643</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1779509344969</v>
+        <v>1780022960736</v>
       </c>
       <c r="C59" t="n">
-        <v>87907</v>
+        <v>75189</v>
       </c>
       <c r="D59" t="n">
-        <v>121.53</v>
+        <v>-842.89</v>
       </c>
       <c r="E59" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="F59" t="n">
-        <v>765</v>
+        <v>939</v>
       </c>
       <c r="G59" t="n">
-        <v>52.25</v>
+        <v>260.25</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I59" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J59" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K59" t="n">
+        <v>906</v>
+      </c>
+      <c r="L59" t="n">
+        <v>112</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.998</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:09.664</t>
+          <t>2026-05-29 09:49:22.115</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1779509345170</v>
+        <v>1780022960936</v>
       </c>
       <c r="C60" t="n">
-        <v>88106</v>
+        <v>74710</v>
       </c>
       <c r="D60" t="n">
-        <v>314.45</v>
+        <v>-1279.74</v>
       </c>
       <c r="E60" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="F60" t="n">
-        <v>685</v>
+        <v>939</v>
       </c>
       <c r="G60" t="n">
-        <v>51.02</v>
+        <v>260.25</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I60" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="J60" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1177</v>
+      </c>
+      <c r="L60" t="n">
+        <v>117</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1.658</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:09.938</t>
+          <t>2026-05-29 09:49:22.160</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1779509345372</v>
+        <v>1780022961136</v>
       </c>
       <c r="C61" t="n">
-        <v>87600</v>
+        <v>75204</v>
       </c>
       <c r="D61" t="n">
-        <v>-207.27</v>
+        <v>-721.76</v>
       </c>
       <c r="E61" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="F61" t="n">
-        <v>685</v>
+        <v>939</v>
       </c>
       <c r="G61" t="n">
-        <v>51.02</v>
+        <v>260.25</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I61" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J61" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1023</v>
+      </c>
+      <c r="L61" t="n">
+        <v>111</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.959</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:09.939</t>
+          <t>2026-05-29 09:49:22.498</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1779509345573</v>
+        <v>1780022961337</v>
       </c>
       <c r="C62" t="n">
-        <v>87736</v>
+        <v>74794</v>
       </c>
       <c r="D62" t="n">
-        <v>-60.91</v>
+        <v>-1095.67</v>
       </c>
       <c r="E62" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="F62" t="n">
-        <v>685</v>
+        <v>939</v>
       </c>
       <c r="G62" t="n">
-        <v>51.02</v>
+        <v>260.25</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I62" t="n">
+        <v>49.84</v>
+      </c>
+      <c r="J62" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1159</v>
+      </c>
+      <c r="L62" t="n">
+        <v>104</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1.141</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:09.940</t>
+          <t>2026-05-29 09:49:22.499</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1779509345774</v>
+        <v>1780022961536</v>
       </c>
       <c r="C63" t="n">
-        <v>87851</v>
+        <v>74884</v>
       </c>
       <c r="D63" t="n">
-        <v>57.14</v>
+        <v>-950.89</v>
       </c>
       <c r="E63" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="F63" t="n">
-        <v>685</v>
+        <v>939</v>
       </c>
       <c r="G63" t="n">
-        <v>51.02</v>
+        <v>260.25</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I63" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J63" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="K63" t="n">
+        <v>962</v>
+      </c>
+      <c r="L63" t="n">
+        <v>113</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.922</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:10.232</t>
+          <t>2026-05-29 09:49:22.500</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1779509345976</v>
+        <v>1780022961736</v>
       </c>
       <c r="C64" t="n">
-        <v>87634</v>
+        <v>74990</v>
       </c>
       <c r="D64" t="n">
-        <v>-162.72</v>
+        <v>-797.34</v>
       </c>
       <c r="E64" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="F64" t="n">
-        <v>785</v>
+        <v>939</v>
       </c>
       <c r="G64" t="n">
-        <v>49.72</v>
+        <v>260.25</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I64" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J64" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K64" t="n">
+        <v>763</v>
+      </c>
+      <c r="L64" t="n">
+        <v>97</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.858</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:10.237</t>
+          <t>2026-05-29 09:49:22.936</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1779509346177</v>
+        <v>1780022961936</v>
       </c>
       <c r="C65" t="n">
-        <v>87502</v>
+        <v>74707</v>
       </c>
       <c r="D65" t="n">
-        <v>-286.58</v>
+        <v>-1040.47</v>
       </c>
       <c r="E65" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="F65" t="n">
-        <v>785</v>
+        <v>3319</v>
       </c>
       <c r="G65" t="n">
-        <v>49.72</v>
+        <v>260.25</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I65" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J65" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K65" t="n">
+        <v>999</v>
+      </c>
+      <c r="L65" t="n">
+        <v>116</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.963</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:10.496</t>
+          <t>2026-05-29 09:49:22.950</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1779509346379</v>
+        <v>1780022962136</v>
       </c>
       <c r="C66" t="n">
-        <v>87679</v>
+        <v>74852</v>
       </c>
       <c r="D66" t="n">
-        <v>-95.26000000000001</v>
+        <v>-843.45</v>
       </c>
       <c r="E66" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="F66" t="n">
-        <v>785</v>
+        <v>3319</v>
       </c>
       <c r="G66" t="n">
-        <v>49.72</v>
+        <v>260.25</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I66" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J66" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K66" t="n">
+        <v>813</v>
+      </c>
+      <c r="L66" t="n">
+        <v>108</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1.128</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:10.784</t>
+          <t>2026-05-29 09:49:23.374</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1779509346580</v>
+        <v>1780022962355</v>
       </c>
       <c r="C67" t="n">
-        <v>87763</v>
+        <v>75011</v>
       </c>
       <c r="D67" t="n">
-        <v>-6.49</v>
+        <v>-642.28</v>
       </c>
       <c r="E67" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="F67" t="n">
-        <v>785</v>
+        <v>3319</v>
       </c>
       <c r="G67" t="n">
-        <v>49.72</v>
+        <v>260.25</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I67" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J67" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1018</v>
+      </c>
+      <c r="L67" t="n">
+        <v>117</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.849</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:11.444</t>
+          <t>2026-05-29 09:49:23.375</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1779509346781</v>
+        <v>1780022962555</v>
       </c>
       <c r="C68" t="n">
-        <v>87549</v>
+        <v>75146</v>
       </c>
       <c r="D68" t="n">
-        <v>-220.17</v>
+        <v>-475.16</v>
       </c>
       <c r="E68" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="F68" t="n">
-        <v>785</v>
+        <v>519</v>
       </c>
       <c r="G68" t="n">
-        <v>55.45</v>
+        <v>263.68</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I68" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J68" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K68" t="n">
+        <v>819</v>
+      </c>
+      <c r="L68" t="n">
+        <v>103</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.768</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:11.710</t>
+          <t>2026-05-29 09:49:23.762</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1779509346983</v>
+        <v>1780022962755</v>
       </c>
       <c r="C69" t="n">
-        <v>87442</v>
+        <v>74854</v>
       </c>
       <c r="D69" t="n">
-        <v>-316.16</v>
+        <v>-743.41</v>
       </c>
       <c r="E69" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="F69" t="n">
-        <v>785</v>
+        <v>519</v>
       </c>
       <c r="G69" t="n">
-        <v>55.45</v>
+        <v>263.68</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I69" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J69" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1006</v>
+      </c>
+      <c r="L69" t="n">
+        <v>106</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1.138</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:11.711</t>
+          <t>2026-05-29 09:49:23.776</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1779509347184</v>
+        <v>1780022962955</v>
       </c>
       <c r="C70" t="n">
-        <v>87965</v>
+        <v>75158</v>
       </c>
       <c r="D70" t="n">
-        <v>222.65</v>
+        <v>-402.24</v>
       </c>
       <c r="E70" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="F70" t="n">
-        <v>785</v>
+        <v>519</v>
       </c>
       <c r="G70" t="n">
-        <v>55.45</v>
+        <v>263.68</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I70" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J70" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K70" t="n">
+        <v>820</v>
+      </c>
+      <c r="L70" t="n">
+        <v>104</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1.103</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:11.714</t>
+          <t>2026-05-29 09:49:24.110</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1779509347385</v>
+        <v>1780022963155</v>
       </c>
       <c r="C71" t="n">
-        <v>87698</v>
+        <v>75776</v>
       </c>
       <c r="D71" t="n">
-        <v>-55.48</v>
+        <v>235.88</v>
       </c>
       <c r="E71" t="n">
         <v>83</v>
       </c>
       <c r="F71" t="n">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="G71" t="n">
-        <v>55.45</v>
+        <v>267.94</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I71" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J71" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K71" t="n">
+        <v>954</v>
+      </c>
+      <c r="L71" t="n">
+        <v>107</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.732</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:11.982</t>
+          <t>2026-05-29 09:49:24.131</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1779509347587</v>
+        <v>1780022963355</v>
       </c>
       <c r="C72" t="n">
-        <v>87675</v>
+        <v>74773</v>
       </c>
       <c r="D72" t="n">
-        <v>-75.70999999999999</v>
+        <v>-778.92</v>
       </c>
       <c r="E72" t="n">
         <v>83</v>
       </c>
       <c r="F72" t="n">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="G72" t="n">
-        <v>55.45</v>
+        <v>267.94</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I72" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J72" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K72" t="n">
+        <v>775</v>
+      </c>
+      <c r="L72" t="n">
+        <v>106</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.5620000000000001</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:11.983</t>
+          <t>2026-05-29 09:49:24.526</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1779509347788</v>
+        <v>1780022963555</v>
       </c>
       <c r="C73" t="n">
-        <v>87663</v>
+        <v>76199</v>
       </c>
       <c r="D73" t="n">
-        <v>-83.92</v>
+        <v>686.03</v>
       </c>
       <c r="E73" t="n">
         <v>83</v>
       </c>
       <c r="F73" t="n">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="G73" t="n">
-        <v>55.45</v>
+        <v>267.94</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I73" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J73" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K73" t="n">
+        <v>970</v>
+      </c>
+      <c r="L73" t="n">
+        <v>108</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.883</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:11.985</t>
+          <t>2026-05-29 09:49:24.527</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1779509347989</v>
+        <v>1780022963755</v>
       </c>
       <c r="C74" t="n">
-        <v>87906</v>
+        <v>75713</v>
       </c>
       <c r="D74" t="n">
-        <v>163.27</v>
+        <v>165.73</v>
       </c>
       <c r="E74" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F74" t="n">
-        <v>685</v>
+        <v>560</v>
       </c>
       <c r="G74" t="n">
-        <v>55.91</v>
+        <v>271</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I74" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J74" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K74" t="n">
+        <v>771</v>
+      </c>
+      <c r="L74" t="n">
+        <v>105</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.946</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:12.336</t>
+          <t>2026-05-29 09:49:24.966</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1779509348191</v>
+        <v>1780022963955</v>
       </c>
       <c r="C75" t="n">
-        <v>87490</v>
+        <v>75516</v>
       </c>
       <c r="D75" t="n">
-        <v>-260.89</v>
+        <v>-39.56</v>
       </c>
       <c r="E75" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F75" t="n">
-        <v>685</v>
+        <v>560</v>
       </c>
       <c r="G75" t="n">
-        <v>55.91</v>
+        <v>271</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I75" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J75" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1010</v>
+      </c>
+      <c r="L75" t="n">
+        <v>106</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.227</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:12.624</t>
+          <t>2026-05-29 09:49:24.969</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1779509348392</v>
+        <v>1780022964155</v>
       </c>
       <c r="C76" t="n">
-        <v>87586</v>
+        <v>75583</v>
       </c>
       <c r="D76" t="n">
-        <v>-151.85</v>
+        <v>29.42</v>
       </c>
       <c r="E76" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F76" t="n">
-        <v>685</v>
+        <v>560</v>
       </c>
       <c r="G76" t="n">
-        <v>55.91</v>
+        <v>271</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I76" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J76" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K76" t="n">
+        <v>813</v>
+      </c>
+      <c r="L76" t="n">
+        <v>105</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1.404</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:12.856</t>
+          <t>2026-05-29 09:49:25.420</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1779509348594</v>
+        <v>1780022964374</v>
       </c>
       <c r="C77" t="n">
-        <v>87818</v>
+        <v>77187</v>
       </c>
       <c r="D77" t="n">
-        <v>87.75</v>
+        <v>1631.95</v>
       </c>
       <c r="E77" t="n">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="F77" t="n">
-        <v>685</v>
+        <v>719</v>
       </c>
       <c r="G77" t="n">
-        <v>55.91</v>
+        <v>269.09</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I77" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J77" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1045</v>
+      </c>
+      <c r="L77" t="n">
+        <v>111</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.6919999999999999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:12.872</t>
+          <t>2026-05-29 09:49:25.437</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1779509348795</v>
+        <v>1780022964574</v>
       </c>
       <c r="C78" t="n">
-        <v>87628</v>
+        <v>75241</v>
       </c>
       <c r="D78" t="n">
-        <v>-106.64</v>
+        <v>-395.65</v>
       </c>
       <c r="E78" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="F78" t="n">
-        <v>745</v>
+        <v>719</v>
       </c>
       <c r="G78" t="n">
-        <v>51.89</v>
+        <v>269.09</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I78" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J78" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K78" t="n">
+        <v>862</v>
+      </c>
+      <c r="L78" t="n">
+        <v>112</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:13.644</t>
+          <t>2026-05-29 09:49:25.640</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1779509348996</v>
+        <v>1780022964774</v>
       </c>
       <c r="C79" t="n">
-        <v>87445</v>
+        <v>75090</v>
       </c>
       <c r="D79" t="n">
-        <v>-284.31</v>
+        <v>-526.87</v>
       </c>
       <c r="E79" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="F79" t="n">
-        <v>745</v>
+        <v>719</v>
       </c>
       <c r="G79" t="n">
-        <v>51.89</v>
+        <v>269.09</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I79" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J79" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K79" t="n">
+        <v>865</v>
+      </c>
+      <c r="L79" t="n">
+        <v>117</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.633</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:13.901</t>
+          <t>2026-05-29 09:49:25.983</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1779509349198</v>
+        <v>1780022964974</v>
       </c>
       <c r="C80" t="n">
-        <v>87640</v>
+        <v>74904</v>
       </c>
       <c r="D80" t="n">
-        <v>-75.09</v>
+        <v>-686.52</v>
       </c>
       <c r="E80" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="F80" t="n">
-        <v>745</v>
+        <v>719</v>
       </c>
       <c r="G80" t="n">
-        <v>51.89</v>
+        <v>269.09</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I80" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J80" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1007</v>
+      </c>
+      <c r="L80" t="n">
+        <v>108</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1.815</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:13.902</t>
+          <t>2026-05-29 09:49:25.997</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1779509349399</v>
+        <v>1780022965174</v>
       </c>
       <c r="C81" t="n">
-        <v>87675</v>
+        <v>74880</v>
       </c>
       <c r="D81" t="n">
-        <v>-36.34</v>
+        <v>-676.2</v>
       </c>
       <c r="E81" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="F81" t="n">
-        <v>705</v>
+        <v>719</v>
       </c>
       <c r="G81" t="n">
-        <v>52.01</v>
+        <v>269.09</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I81" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J81" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K81" t="n">
+        <v>821</v>
+      </c>
+      <c r="L81" t="n">
+        <v>110</v>
+      </c>
+      <c r="M81" t="n">
+        <v>2.396</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:13.902</t>
+          <t>2026-05-29 09:49:26.416</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1779509349600</v>
+        <v>1780022965374</v>
       </c>
       <c r="C82" t="n">
-        <v>87282</v>
+        <v>74808</v>
       </c>
       <c r="D82" t="n">
-        <v>-427.52</v>
+        <v>-714.39</v>
       </c>
       <c r="E82" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="F82" t="n">
-        <v>705</v>
+        <v>719</v>
       </c>
       <c r="G82" t="n">
-        <v>52.01</v>
+        <v>269.09</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I82" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J82" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K82" t="n">
+        <v>1041</v>
+      </c>
+      <c r="L82" t="n">
+        <v>108</v>
+      </c>
+      <c r="M82" t="n">
+        <v>1.341</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:14.430</t>
+          <t>2026-05-29 09:49:26.418</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1779509349802</v>
+        <v>1780022965574</v>
       </c>
       <c r="C83" t="n">
-        <v>87484</v>
+        <v>74887</v>
       </c>
       <c r="D83" t="n">
-        <v>-204.15</v>
+        <v>-599.67</v>
       </c>
       <c r="E83" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="F83" t="n">
-        <v>705</v>
+        <v>719</v>
       </c>
       <c r="G83" t="n">
-        <v>52.01</v>
+        <v>269.09</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I83" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J83" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K83" t="n">
+        <v>843</v>
+      </c>
+      <c r="L83" t="n">
+        <v>114</v>
+      </c>
+      <c r="M83" t="n">
+        <v>1.332</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:14.697</t>
+          <t>2026-05-29 09:49:26.820</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1779509350003</v>
+        <v>1780022965774</v>
       </c>
       <c r="C84" t="n">
-        <v>87663</v>
+        <v>74776</v>
       </c>
       <c r="D84" t="n">
-        <v>-14.94</v>
+        <v>-680.6799999999999</v>
       </c>
       <c r="E84" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="F84" t="n">
-        <v>624</v>
+        <v>719</v>
       </c>
       <c r="G84" t="n">
-        <v>59.79</v>
+        <v>269.09</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I84" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J84" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1044</v>
+      </c>
+      <c r="L84" t="n">
+        <v>114</v>
+      </c>
+      <c r="M84" t="n">
+        <v>1.297</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:14.698</t>
+          <t>2026-05-29 09:49:26.821</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1779509350205</v>
+        <v>1780022965974</v>
       </c>
       <c r="C85" t="n">
-        <v>87037</v>
+        <v>74498</v>
       </c>
       <c r="D85" t="n">
-        <v>-640.1900000000001</v>
+        <v>-924.65</v>
       </c>
       <c r="E85" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="F85" t="n">
-        <v>624</v>
+        <v>719</v>
       </c>
       <c r="G85" t="n">
-        <v>59.79</v>
+        <v>269.09</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I85" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J85" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K85" t="n">
+        <v>846</v>
+      </c>
+      <c r="L85" t="n">
+        <v>113</v>
+      </c>
+      <c r="M85" t="n">
+        <v>1.272</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:14.700</t>
+          <t>2026-05-29 09:49:27.246</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1779509350406</v>
+        <v>1780022966174</v>
       </c>
       <c r="C86" t="n">
-        <v>87209</v>
+        <v>74644</v>
       </c>
       <c r="D86" t="n">
-        <v>-436.18</v>
+        <v>-732.42</v>
       </c>
       <c r="E86" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="F86" t="n">
-        <v>624</v>
+        <v>719</v>
       </c>
       <c r="G86" t="n">
-        <v>59.79</v>
+        <v>269.09</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I86" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J86" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K86" t="n">
+        <v>1070</v>
+      </c>
+      <c r="L86" t="n">
+        <v>113</v>
+      </c>
+      <c r="M86" t="n">
+        <v>1.622</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:14.976</t>
+          <t>2026-05-29 09:49:27.248</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1779509350607</v>
+        <v>1780022966393</v>
       </c>
       <c r="C87" t="n">
-        <v>87452</v>
+        <v>74454</v>
       </c>
       <c r="D87" t="n">
-        <v>-171.37</v>
+        <v>-885.8</v>
       </c>
       <c r="E87" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="F87" t="n">
-        <v>624</v>
+        <v>719</v>
       </c>
       <c r="G87" t="n">
-        <v>59.79</v>
+        <v>269.09</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I87" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J87" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K87" t="n">
+        <v>854</v>
+      </c>
+      <c r="L87" t="n">
+        <v>131</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1.741</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:14.978</t>
+          <t>2026-05-29 09:49:27.663</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1779509350809</v>
+        <v>1780022966593</v>
       </c>
       <c r="C88" t="n">
-        <v>87536</v>
+        <v>74398</v>
       </c>
       <c r="D88" t="n">
-        <v>-78.8</v>
+        <v>-897.51</v>
       </c>
       <c r="E88" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="F88" t="n">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="G88" t="n">
-        <v>59.36</v>
+        <v>269.09</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I88" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J88" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K88" t="n">
+        <v>1068</v>
+      </c>
+      <c r="L88" t="n">
+        <v>112</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1.761</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:15.706</t>
+          <t>2026-05-29 09:49:27.666</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1779509351010</v>
+        <v>1780022966793</v>
       </c>
       <c r="C89" t="n">
-        <v>87273</v>
+        <v>74154</v>
       </c>
       <c r="D89" t="n">
-        <v>-337.86</v>
+        <v>-1096.63</v>
       </c>
       <c r="E89" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="F89" t="n">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="G89" t="n">
-        <v>59.36</v>
+        <v>269.09</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I89" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J89" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K89" t="n">
+        <v>872</v>
+      </c>
+      <c r="L89" t="n">
+        <v>113</v>
+      </c>
+      <c r="M89" t="n">
+        <v>1.509</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:15.946</t>
+          <t>2026-05-29 09:49:28.069</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1779509351211</v>
+        <v>1780022966993</v>
       </c>
       <c r="C90" t="n">
-        <v>87386</v>
+        <v>74830</v>
       </c>
       <c r="D90" t="n">
-        <v>-207.97</v>
+        <v>-365.8</v>
       </c>
       <c r="E90" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="F90" t="n">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="G90" t="n">
-        <v>59.36</v>
+        <v>269.09</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I90" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J90" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1075</v>
+      </c>
+      <c r="L90" t="n">
+        <v>109</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1.192</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:15.947</t>
+          <t>2026-05-29 09:49:28.071</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1779509351413</v>
+        <v>1780022967193</v>
       </c>
       <c r="C91" t="n">
-        <v>87566</v>
+        <v>74397</v>
       </c>
       <c r="D91" t="n">
-        <v>-17.57</v>
+        <v>-780.51</v>
       </c>
       <c r="E91" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="F91" t="n">
-        <v>644</v>
+        <v>719</v>
       </c>
       <c r="G91" t="n">
-        <v>59.87</v>
+        <v>269.09</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I91" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J91" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K91" t="n">
+        <v>877</v>
+      </c>
+      <c r="L91" t="n">
+        <v>113</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.966</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:15.952</t>
+          <t>2026-05-29 09:49:28.412</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1779509351614</v>
+        <v>1780022967393</v>
       </c>
       <c r="C92" t="n">
-        <v>87080</v>
+        <v>74035</v>
       </c>
       <c r="D92" t="n">
-        <v>-502.69</v>
+        <v>-1103.48</v>
       </c>
       <c r="E92" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="F92" t="n">
-        <v>644</v>
+        <v>719</v>
       </c>
       <c r="G92" t="n">
-        <v>59.87</v>
+        <v>269.09</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I92" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J92" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K92" t="n">
+        <v>1018</v>
+      </c>
+      <c r="L92" t="n">
+        <v>118</v>
+      </c>
+      <c r="M92" t="n">
+        <v>1.424</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:16.234</t>
+          <t>2026-05-29 09:49:28.414</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1779509351815</v>
+        <v>1780022967593</v>
       </c>
       <c r="C93" t="n">
-        <v>87387</v>
+        <v>73940</v>
       </c>
       <c r="D93" t="n">
-        <v>-170.56</v>
+        <v>-1143.31</v>
       </c>
       <c r="E93" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="F93" t="n">
-        <v>644</v>
+        <v>719</v>
       </c>
       <c r="G93" t="n">
-        <v>59.87</v>
+        <v>269.09</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I93" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J93" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K93" t="n">
+        <v>820</v>
+      </c>
+      <c r="L93" t="n">
+        <v>110</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0.705</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:16.493</t>
+          <t>2026-05-29 09:49:28.839</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1779509352017</v>
+        <v>1780022967793</v>
       </c>
       <c r="C94" t="n">
-        <v>87503</v>
+        <v>73584</v>
       </c>
       <c r="D94" t="n">
-        <v>-46.03</v>
+        <v>-1442.15</v>
       </c>
       <c r="E94" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="F94" t="n">
-        <v>645</v>
+        <v>719</v>
       </c>
       <c r="G94" t="n">
-        <v>62.32</v>
+        <v>269.09</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I94" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J94" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K94" t="n">
+        <v>1045</v>
+      </c>
+      <c r="L94" t="n">
+        <v>112</v>
+      </c>
+      <c r="M94" t="n">
+        <v>1.248</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:16.494</t>
+          <t>2026-05-29 09:49:28.869</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1779509352218</v>
+        <v>1780022967993</v>
       </c>
       <c r="C95" t="n">
-        <v>87393</v>
+        <v>73547</v>
       </c>
       <c r="D95" t="n">
-        <v>-153.73</v>
+        <v>-1407.04</v>
       </c>
       <c r="E95" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="F95" t="n">
-        <v>645</v>
+        <v>719</v>
       </c>
       <c r="G95" t="n">
-        <v>62.32</v>
+        <v>269.09</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I95" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J95" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K95" t="n">
+        <v>875</v>
+      </c>
+      <c r="L95" t="n">
+        <v>116</v>
+      </c>
+      <c r="M95" t="n">
+        <v>1.358</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:16.949</t>
+          <t>2026-05-29 09:49:29.348</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1779509352419</v>
+        <v>1780022968193</v>
       </c>
       <c r="C96" t="n">
-        <v>87102</v>
+        <v>74199</v>
       </c>
       <c r="D96" t="n">
-        <v>-437.04</v>
+        <v>-684.6900000000001</v>
       </c>
       <c r="E96" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="F96" t="n">
-        <v>645</v>
+        <v>719</v>
       </c>
       <c r="G96" t="n">
-        <v>62.32</v>
+        <v>269.09</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I96" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J96" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1154</v>
+      </c>
+      <c r="L96" t="n">
+        <v>116</v>
+      </c>
+      <c r="M96" t="n">
+        <v>1.178</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:17.211</t>
+          <t>2026-05-29 09:49:29.350</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1779509352621</v>
+        <v>1780022968412</v>
       </c>
       <c r="C97" t="n">
-        <v>87240</v>
+        <v>74155</v>
       </c>
       <c r="D97" t="n">
-        <v>-277.19</v>
+        <v>-694.45</v>
       </c>
       <c r="E97" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="F97" t="n">
-        <v>645</v>
+        <v>3918</v>
       </c>
       <c r="G97" t="n">
-        <v>62.32</v>
+        <v>269.09</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I97" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J97" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K97" t="n">
+        <v>937</v>
+      </c>
+      <c r="L97" t="n">
+        <v>116</v>
+      </c>
+      <c r="M97" t="n">
+        <v>1.05</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:17.219</t>
+          <t>2026-05-29 09:49:29.695</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1779509352822</v>
+        <v>1780022968612</v>
       </c>
       <c r="C98" t="n">
-        <v>87645</v>
+        <v>73753</v>
       </c>
       <c r="D98" t="n">
-        <v>141.67</v>
+        <v>-1061.73</v>
       </c>
       <c r="E98" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="F98" t="n">
-        <v>805</v>
+        <v>3918</v>
       </c>
       <c r="G98" t="n">
-        <v>65.7</v>
+        <v>269.09</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I98" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J98" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K98" t="n">
+        <v>1080</v>
+      </c>
+      <c r="L98" t="n">
+        <v>118</v>
+      </c>
+      <c r="M98" t="n">
+        <v>2.054</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:17.250</t>
+          <t>2026-05-29 09:49:29.697</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1779509353023</v>
+        <v>1780022968812</v>
       </c>
       <c r="C99" t="n">
-        <v>87004</v>
+        <v>74174</v>
       </c>
       <c r="D99" t="n">
-        <v>-506.42</v>
+        <v>-587.64</v>
       </c>
       <c r="E99" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="F99" t="n">
-        <v>805</v>
+        <v>3918</v>
       </c>
       <c r="G99" t="n">
-        <v>65.7</v>
+        <v>269.09</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I99" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J99" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K99" t="n">
+        <v>883</v>
+      </c>
+      <c r="L99" t="n">
+        <v>115</v>
+      </c>
+      <c r="M99" t="n">
+        <v>2.3</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:17.488</t>
+          <t>2026-05-29 09:49:30.043</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1779509353225</v>
+        <v>1780022969012</v>
       </c>
       <c r="C100" t="n">
-        <v>87008</v>
+        <v>73986</v>
       </c>
       <c r="D100" t="n">
-        <v>-477.09</v>
+        <v>-746.26</v>
       </c>
       <c r="E100" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F100" t="n">
-        <v>805</v>
+        <v>680</v>
       </c>
       <c r="G100" t="n">
-        <v>65.7</v>
+        <v>267.24</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I100" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J100" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K100" t="n">
+        <v>1029</v>
+      </c>
+      <c r="L100" t="n">
+        <v>106</v>
+      </c>
+      <c r="M100" t="n">
+        <v>1.42</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:17.735</t>
+          <t>2026-05-29 09:49:30.045</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1779509353426</v>
+        <v>1780022969212</v>
       </c>
       <c r="C101" t="n">
-        <v>87014</v>
+        <v>74109</v>
       </c>
       <c r="D101" t="n">
-        <v>-447.24</v>
+        <v>-585.95</v>
       </c>
       <c r="E101" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F101" t="n">
-        <v>805</v>
+        <v>680</v>
       </c>
       <c r="G101" t="n">
-        <v>65.7</v>
+        <v>267.24</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I101" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J101" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K101" t="n">
+        <v>832</v>
+      </c>
+      <c r="L101" t="n">
+        <v>105</v>
+      </c>
+      <c r="M101" t="n">
+        <v>1.522</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:18.255</t>
+          <t>2026-05-29 09:49:30.480</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1779509353628</v>
+        <v>1780022969412</v>
       </c>
       <c r="C102" t="n">
-        <v>86346</v>
+        <v>74235</v>
       </c>
       <c r="D102" t="n">
-        <v>-1092.88</v>
+        <v>-430.65</v>
       </c>
       <c r="E102" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F102" t="n">
-        <v>805</v>
+        <v>680</v>
       </c>
       <c r="G102" t="n">
-        <v>65.7</v>
+        <v>267.24</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I102" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J102" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K102" t="n">
+        <v>1066</v>
+      </c>
+      <c r="L102" t="n">
+        <v>106</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0.994</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:18.551</t>
+          <t>2026-05-29 09:49:30.688</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1779509353829</v>
+        <v>1780022969612</v>
       </c>
       <c r="C103" t="n">
-        <v>86712</v>
+        <v>73924</v>
       </c>
       <c r="D103" t="n">
-        <v>-672.23</v>
+        <v>-720.12</v>
       </c>
       <c r="E103" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F103" t="n">
-        <v>805</v>
+        <v>680</v>
       </c>
       <c r="G103" t="n">
-        <v>65.7</v>
+        <v>267.24</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I103" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J103" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K103" t="n">
+        <v>1075</v>
+      </c>
+      <c r="L103" t="n">
+        <v>109</v>
+      </c>
+      <c r="M103" t="n">
+        <v>1.135</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:18.552</t>
+          <t>2026-05-29 09:49:30.911</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1779509354030</v>
+        <v>1780022969812</v>
       </c>
       <c r="C104" t="n">
-        <v>86958</v>
+        <v>73764</v>
       </c>
       <c r="D104" t="n">
-        <v>-392.62</v>
+        <v>-844.11</v>
       </c>
       <c r="E104" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F104" t="n">
-        <v>805</v>
+        <v>680</v>
       </c>
       <c r="G104" t="n">
-        <v>65.7</v>
+        <v>267.24</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I104" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J104" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K104" t="n">
+        <v>1098</v>
+      </c>
+      <c r="L104" t="n">
+        <v>108</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0.518</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:18.553</t>
+          <t>2026-05-29 09:49:30.912</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1779509354232</v>
+        <v>1780022970012</v>
       </c>
       <c r="C105" t="n">
-        <v>86653</v>
+        <v>73977</v>
       </c>
       <c r="D105" t="n">
-        <v>-677.99</v>
+        <v>-588.91</v>
       </c>
       <c r="E105" t="n">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="F105" t="n">
-        <v>1249</v>
+        <v>680</v>
       </c>
       <c r="G105" t="n">
-        <v>186.4</v>
+        <v>267.24</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I105" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J105" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K105" t="n">
+        <v>899</v>
+      </c>
+      <c r="L105" t="n">
+        <v>107</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0.976</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:19.006</t>
+          <t>2026-05-29 09:49:31.507</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1779509354433</v>
+        <v>1780022970232</v>
       </c>
       <c r="C106" t="n">
-        <v>86630</v>
+        <v>73633</v>
       </c>
       <c r="D106" t="n">
-        <v>-667.09</v>
+        <v>-903.46</v>
       </c>
       <c r="E106" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F106" t="n">
-        <v>1249</v>
+        <v>1279</v>
       </c>
       <c r="G106" t="n">
-        <v>186.4</v>
+        <v>311.74</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I106" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="J106" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K106" t="n">
+        <v>1273</v>
+      </c>
+      <c r="L106" t="n">
+        <v>105</v>
+      </c>
+      <c r="M106" t="n">
+        <v>2.166</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:19.264</t>
+          <t>2026-05-29 09:49:31.519</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1779509354634</v>
+        <v>1780022970431</v>
       </c>
       <c r="C107" t="n">
-        <v>86846</v>
+        <v>73795</v>
       </c>
       <c r="D107" t="n">
-        <v>-417.74</v>
+        <v>-696.29</v>
       </c>
       <c r="E107" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F107" t="n">
-        <v>1249</v>
+        <v>1279</v>
       </c>
       <c r="G107" t="n">
-        <v>186.4</v>
+        <v>311.74</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I107" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J107" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K107" t="n">
+        <v>1087</v>
+      </c>
+      <c r="L107" t="n">
+        <v>106</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0.584</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:19.265</t>
+          <t>2026-05-29 09:49:31.521</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1779509354836</v>
+        <v>1780022970631</v>
       </c>
       <c r="C108" t="n">
-        <v>86824</v>
+        <v>74119</v>
       </c>
       <c r="D108" t="n">
-        <v>-418.85</v>
+        <v>-337.47</v>
       </c>
       <c r="E108" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F108" t="n">
-        <v>644</v>
+        <v>1279</v>
       </c>
       <c r="G108" t="n">
-        <v>185.06</v>
+        <v>311.74</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I108" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J108" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K108" t="n">
+        <v>888</v>
+      </c>
+      <c r="L108" t="n">
+        <v>107</v>
+      </c>
+      <c r="M108" t="n">
+        <v>1.668</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:19.265</t>
+          <t>2026-05-29 09:49:31.893</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1779509355037</v>
+        <v>1780022970831</v>
       </c>
       <c r="C109" t="n">
-        <v>86450</v>
+        <v>74775</v>
       </c>
       <c r="D109" t="n">
-        <v>-771.91</v>
+        <v>335.4</v>
       </c>
       <c r="E109" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="F109" t="n">
-        <v>644</v>
+        <v>460</v>
       </c>
       <c r="G109" t="n">
-        <v>185.06</v>
+        <v>318.58</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I109" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J109" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K109" t="n">
+        <v>1060</v>
+      </c>
+      <c r="L109" t="n">
+        <v>107</v>
+      </c>
+      <c r="M109" t="n">
+        <v>1.994</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:19.503</t>
+          <t>2026-05-29 09:49:31.895</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1779509355239</v>
+        <v>1780022971031</v>
       </c>
       <c r="C110" t="n">
-        <v>86701</v>
+        <v>74381</v>
       </c>
       <c r="D110" t="n">
-        <v>-482.31</v>
+        <v>-75.37</v>
       </c>
       <c r="E110" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="F110" t="n">
-        <v>644</v>
+        <v>460</v>
       </c>
       <c r="G110" t="n">
-        <v>185.06</v>
+        <v>318.58</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I110" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J110" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K110" t="n">
+        <v>863</v>
+      </c>
+      <c r="L110" t="n">
+        <v>104</v>
+      </c>
+      <c r="M110" t="n">
+        <v>1.275</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:19.541</t>
+          <t>2026-05-29 09:49:32.231</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1779509355440</v>
+        <v>1780022971231</v>
       </c>
       <c r="C111" t="n">
-        <v>87186</v>
+        <v>74788</v>
       </c>
       <c r="D111" t="n">
-        <v>26.8</v>
+        <v>335.4</v>
       </c>
       <c r="E111" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="F111" t="n">
-        <v>705</v>
+        <v>460</v>
       </c>
       <c r="G111" t="n">
-        <v>184.42</v>
+        <v>318.58</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I111" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J111" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K111" t="n">
+        <v>999</v>
+      </c>
+      <c r="L111" t="n">
+        <v>116</v>
+      </c>
+      <c r="M111" t="n">
+        <v>1.174</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:19.920</t>
+          <t>2026-05-29 09:49:32.233</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1779509355641</v>
+        <v>1780022971431</v>
       </c>
       <c r="C112" t="n">
-        <v>86682</v>
+        <v>75114</v>
       </c>
       <c r="D112" t="n">
-        <v>-478.54</v>
+        <v>644.63</v>
       </c>
       <c r="E112" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="F112" t="n">
-        <v>705</v>
+        <v>460</v>
       </c>
       <c r="G112" t="n">
-        <v>184.42</v>
+        <v>318.58</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I112" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J112" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="K112" t="n">
+        <v>801</v>
+      </c>
+      <c r="L112" t="n">
+        <v>106</v>
+      </c>
+      <c r="M112" t="n">
+        <v>1.325</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:20.191</t>
+          <t>2026-05-29 09:49:32.572</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1779509355843</v>
+        <v>1780022971631</v>
       </c>
       <c r="C113" t="n">
-        <v>86701</v>
+        <v>74773</v>
       </c>
       <c r="D113" t="n">
-        <v>-435.61</v>
+        <v>271.4</v>
       </c>
       <c r="E113" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="F113" t="n">
-        <v>705</v>
+        <v>460</v>
       </c>
       <c r="G113" t="n">
-        <v>184.42</v>
+        <v>318.58</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I113" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J113" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K113" t="n">
+        <v>940</v>
+      </c>
+      <c r="L113" t="n">
+        <v>105</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0.803</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:20.197</t>
+          <t>2026-05-29 09:49:32.912</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>1779509356044</v>
+        <v>1780022971831</v>
       </c>
       <c r="C114" t="n">
-        <v>86760</v>
+        <v>74956</v>
       </c>
       <c r="D114" t="n">
-        <v>-354.83</v>
+        <v>440.83</v>
       </c>
       <c r="E114" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="F114" t="n">
-        <v>705</v>
+        <v>460</v>
       </c>
       <c r="G114" t="n">
-        <v>184.42</v>
+        <v>318.58</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I114" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J114" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K114" t="n">
+        <v>1079</v>
+      </c>
+      <c r="L114" t="n">
+        <v>108</v>
+      </c>
+      <c r="M114" t="n">
+        <v>1.24</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:20.485</t>
+          <t>2026-05-29 09:49:32.913</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1779509356245</v>
+        <v>1780022972031</v>
       </c>
       <c r="C115" t="n">
-        <v>86610</v>
+        <v>75342</v>
       </c>
       <c r="D115" t="n">
-        <v>-487.09</v>
+        <v>804.79</v>
       </c>
       <c r="E115" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="F115" t="n">
-        <v>705</v>
+        <v>460</v>
       </c>
       <c r="G115" t="n">
-        <v>184.42</v>
+        <v>318.58</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I115" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J115" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K115" t="n">
+        <v>881</v>
+      </c>
+      <c r="L115" t="n">
+        <v>107</v>
+      </c>
+      <c r="M115" t="n">
+        <v>1.042</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:20.497</t>
+          <t>2026-05-29 09:49:33.227</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>1779509356447</v>
+        <v>1780022972251</v>
       </c>
       <c r="C116" t="n">
-        <v>86370</v>
+        <v>75042</v>
       </c>
       <c r="D116" t="n">
-        <v>-702.73</v>
+        <v>464.55</v>
       </c>
       <c r="E116" t="n">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="F116" t="n">
-        <v>886</v>
+        <v>460</v>
       </c>
       <c r="G116" t="n">
-        <v>189.39</v>
+        <v>318.58</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I116" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J116" t="n">
+        <v>34.54</v>
+      </c>
+      <c r="K116" t="n">
+        <v>975</v>
+      </c>
+      <c r="L116" t="n">
+        <v>110</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0.989</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:20.742</t>
+          <t>2026-05-29 09:49:33.229</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1779509356648</v>
+        <v>1780022972450</v>
       </c>
       <c r="C117" t="n">
-        <v>86389</v>
+        <v>75162</v>
       </c>
       <c r="D117" t="n">
-        <v>-648.6</v>
+        <v>561.3200000000001</v>
       </c>
       <c r="E117" t="n">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="F117" t="n">
-        <v>886</v>
+        <v>460</v>
       </c>
       <c r="G117" t="n">
-        <v>189.39</v>
+        <v>318.58</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I117" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J117" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="K117" t="n">
+        <v>777</v>
+      </c>
+      <c r="L117" t="n">
+        <v>105</v>
+      </c>
+      <c r="M117" t="n">
+        <v>1.543</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:21.013</t>
+          <t>2026-05-29 09:49:33.514</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1779509356849</v>
+        <v>1780022972650</v>
       </c>
       <c r="C118" t="n">
-        <v>86469</v>
+        <v>75276</v>
       </c>
       <c r="D118" t="n">
-        <v>-536.17</v>
+        <v>647.25</v>
       </c>
       <c r="E118" t="n">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="F118" t="n">
-        <v>886</v>
+        <v>1939</v>
       </c>
       <c r="G118" t="n">
-        <v>189.39</v>
+        <v>318.58</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I118" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J118" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K118" t="n">
+        <v>863</v>
+      </c>
+      <c r="L118" t="n">
+        <v>120</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.915</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:21.276</t>
+          <t>2026-05-29 09:49:34.151</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1779509357051</v>
+        <v>1780022972850</v>
       </c>
       <c r="C119" t="n">
-        <v>86320</v>
+        <v>74960</v>
       </c>
       <c r="D119" t="n">
-        <v>-658.36</v>
+        <v>298.89</v>
       </c>
       <c r="E119" t="n">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="F119" t="n">
-        <v>886</v>
+        <v>1939</v>
       </c>
       <c r="G119" t="n">
-        <v>189.39</v>
+        <v>318.58</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I119" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J119" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K119" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L119" t="n">
+        <v>110</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.901</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:21.277</t>
+          <t>2026-05-29 09:49:34.152</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>1779509357252</v>
+        <v>1780022973050</v>
       </c>
       <c r="C120" t="n">
-        <v>86555</v>
+        <v>74834</v>
       </c>
       <c r="D120" t="n">
-        <v>-390.44</v>
+        <v>157.95</v>
       </c>
       <c r="E120" t="n">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="F120" t="n">
-        <v>886</v>
+        <v>1939</v>
       </c>
       <c r="G120" t="n">
-        <v>189.39</v>
+        <v>318.58</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I120" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J120" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1101</v>
+      </c>
+      <c r="L120" t="n">
+        <v>110</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.878</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:21.756</t>
+          <t>2026-05-29 09:49:34.153</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1779509357454</v>
+        <v>1780022973250</v>
       </c>
       <c r="C121" t="n">
-        <v>86828</v>
+        <v>74990</v>
       </c>
       <c r="D121" t="n">
-        <v>-97.92</v>
+        <v>306.05</v>
       </c>
       <c r="E121" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="F121" t="n">
-        <v>1027</v>
+        <v>1939</v>
       </c>
       <c r="G121" t="n">
-        <v>205.12</v>
+        <v>318.58</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I121" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J121" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K121" t="n">
+        <v>902</v>
+      </c>
+      <c r="L121" t="n">
+        <v>109</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.954</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:22.030</t>
+          <t>2026-05-29 09:49:34.557</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>1779509357655</v>
+        <v>1780022973450</v>
       </c>
       <c r="C122" t="n">
-        <v>86551</v>
+        <v>75102</v>
       </c>
       <c r="D122" t="n">
-        <v>-370.02</v>
+        <v>402.75</v>
       </c>
       <c r="E122" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F122" t="n">
-        <v>1027</v>
+        <v>820</v>
       </c>
       <c r="G122" t="n">
-        <v>205.12</v>
+        <v>255.57</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I122" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J122" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K122" t="n">
+        <v>1106</v>
+      </c>
+      <c r="L122" t="n">
+        <v>110</v>
+      </c>
+      <c r="M122" t="n">
+        <v>1.125</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:22.031</t>
+          <t>2026-05-29 09:49:34.559</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>1779509357856</v>
+        <v>1780022973650</v>
       </c>
       <c r="C123" t="n">
-        <v>86686</v>
+        <v>74793</v>
       </c>
       <c r="D123" t="n">
-        <v>-216.52</v>
+        <v>73.61</v>
       </c>
       <c r="E123" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F123" t="n">
-        <v>1027</v>
+        <v>820</v>
       </c>
       <c r="G123" t="n">
-        <v>205.12</v>
+        <v>255.57</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I123" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J123" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K123" t="n">
+        <v>908</v>
+      </c>
+      <c r="L123" t="n">
+        <v>113</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.913</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:22.301</t>
+          <t>2026-05-29 09:49:35.011</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1779509358058</v>
+        <v>1780022973850</v>
       </c>
       <c r="C124" t="n">
-        <v>87061</v>
+        <v>74954</v>
       </c>
       <c r="D124" t="n">
-        <v>169.3</v>
+        <v>230.93</v>
       </c>
       <c r="E124" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F124" t="n">
-        <v>1027</v>
+        <v>820</v>
       </c>
       <c r="G124" t="n">
-        <v>205.12</v>
+        <v>255.57</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I124" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J124" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K124" t="n">
+        <v>1160</v>
+      </c>
+      <c r="L124" t="n">
+        <v>109</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.974</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:22.323</t>
+          <t>2026-05-29 09:49:35.013</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>1779509358259</v>
+        <v>1780022974050</v>
       </c>
       <c r="C125" t="n">
-        <v>87071</v>
+        <v>75065</v>
       </c>
       <c r="D125" t="n">
-        <v>170.84</v>
+        <v>330.38</v>
       </c>
       <c r="E125" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="F125" t="n">
-        <v>1027</v>
+        <v>560</v>
       </c>
       <c r="G125" t="n">
-        <v>205.12</v>
+        <v>245.19</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I125" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J125" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K125" t="n">
+        <v>961</v>
+      </c>
+      <c r="L125" t="n">
+        <v>114</v>
+      </c>
+      <c r="M125" t="n">
+        <v>1.964</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:22.667</t>
+          <t>2026-05-29 09:49:35.494</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>1779509358460</v>
+        <v>1780022974250</v>
       </c>
       <c r="C126" t="n">
-        <v>87145</v>
+        <v>74771</v>
       </c>
       <c r="D126" t="n">
-        <v>236.3</v>
+        <v>19.86</v>
       </c>
       <c r="E126" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="F126" t="n">
-        <v>1027</v>
+        <v>560</v>
       </c>
       <c r="G126" t="n">
-        <v>205.12</v>
+        <v>245.19</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I126" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J126" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K126" t="n">
+        <v>1243</v>
+      </c>
+      <c r="L126" t="n">
+        <v>114</v>
+      </c>
+      <c r="M126" t="n">
+        <v>1.056</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:22.955</t>
+          <t>2026-05-29 09:49:35.496</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1779509358662</v>
+        <v>1780022974469</v>
       </c>
       <c r="C127" t="n">
-        <v>87579</v>
+        <v>74954</v>
       </c>
       <c r="D127" t="n">
-        <v>658.48</v>
+        <v>201.87</v>
       </c>
       <c r="E127" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="F127" t="n">
-        <v>1027</v>
+        <v>560</v>
       </c>
       <c r="G127" t="n">
-        <v>205.12</v>
+        <v>245.19</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I127" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J127" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K127" t="n">
+        <v>1026</v>
+      </c>
+      <c r="L127" t="n">
+        <v>107</v>
+      </c>
+      <c r="M127" t="n">
+        <v>1.339</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:23.490</t>
+          <t>2026-05-29 09:49:35.841</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1779509358863</v>
+        <v>1780022974669</v>
       </c>
       <c r="C128" t="n">
-        <v>88163</v>
+        <v>75143</v>
       </c>
       <c r="D128" t="n">
-        <v>1209.56</v>
+        <v>380.78</v>
       </c>
       <c r="E128" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F128" t="n">
-        <v>1027</v>
+        <v>640</v>
       </c>
       <c r="G128" t="n">
-        <v>205.12</v>
+        <v>232.84</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I128" t="n">
+        <v>46.65</v>
+      </c>
+      <c r="J128" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K128" t="n">
+        <v>1172</v>
+      </c>
+      <c r="L128" t="n">
+        <v>119</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.639</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:23.765</t>
+          <t>2026-05-29 09:49:35.884</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1779509359064</v>
+        <v>1780022974869</v>
       </c>
       <c r="C129" t="n">
-        <v>88568</v>
+        <v>74984</v>
       </c>
       <c r="D129" t="n">
-        <v>1554.08</v>
+        <v>202.74</v>
       </c>
       <c r="E129" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F129" t="n">
-        <v>1027</v>
+        <v>640</v>
       </c>
       <c r="G129" t="n">
-        <v>205.12</v>
+        <v>232.84</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I129" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J129" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K129" t="n">
+        <v>1014</v>
+      </c>
+      <c r="L129" t="n">
+        <v>117</v>
+      </c>
+      <c r="M129" t="n">
+        <v>1.208</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:23.771</t>
+          <t>2026-05-29 09:49:36.196</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>1779509359266</v>
+        <v>1780022975070</v>
       </c>
       <c r="C130" t="n">
-        <v>88783</v>
+        <v>74985</v>
       </c>
       <c r="D130" t="n">
-        <v>1691.38</v>
+        <v>193.6</v>
       </c>
       <c r="E130" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F130" t="n">
-        <v>1027</v>
+        <v>640</v>
       </c>
       <c r="G130" t="n">
-        <v>205.12</v>
+        <v>232.84</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I130" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J130" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K130" t="n">
+        <v>1125</v>
+      </c>
+      <c r="L130" t="n">
+        <v>105</v>
+      </c>
+      <c r="M130" t="n">
+        <v>1.417</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:23.805</t>
+          <t>2026-05-29 09:49:36.257</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>1779509359467</v>
+        <v>1780022975269</v>
       </c>
       <c r="C131" t="n">
-        <v>89156</v>
+        <v>75121</v>
       </c>
       <c r="D131" t="n">
-        <v>1979.81</v>
+        <v>319.92</v>
       </c>
       <c r="E131" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F131" t="n">
-        <v>1027</v>
+        <v>640</v>
       </c>
       <c r="G131" t="n">
-        <v>205.12</v>
+        <v>232.84</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I131" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J131" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K131" t="n">
+        <v>987</v>
+      </c>
+      <c r="L131" t="n">
+        <v>119</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.895</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:24.023</t>
+          <t>2026-05-29 09:49:36.656</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>1779509359669</v>
+        <v>1780022975470</v>
       </c>
       <c r="C132" t="n">
-        <v>89410</v>
+        <v>74816</v>
       </c>
       <c r="D132" t="n">
-        <v>2134.82</v>
+        <v>-1.08</v>
       </c>
       <c r="E132" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="F132" t="n">
-        <v>1027</v>
+        <v>679</v>
       </c>
       <c r="G132" t="n">
-        <v>205.12</v>
+        <v>225.49</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I132" t="n">
+        <v>49.63</v>
+      </c>
+      <c r="J132" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="K132" t="n">
+        <v>1184</v>
+      </c>
+      <c r="L132" t="n">
+        <v>154</v>
+      </c>
+      <c r="M132" t="n">
+        <v>1.406</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:24.032</t>
+          <t>2026-05-29 09:49:36.657</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>1779509359870</v>
+        <v>1780022975669</v>
       </c>
       <c r="C133" t="n">
-        <v>90432</v>
+        <v>74923</v>
       </c>
       <c r="D133" t="n">
-        <v>3050.08</v>
+        <v>105.98</v>
       </c>
       <c r="E133" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="F133" t="n">
-        <v>1027</v>
+        <v>679</v>
       </c>
       <c r="G133" t="n">
-        <v>205.12</v>
+        <v>225.49</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I133" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J133" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="K133" t="n">
+        <v>987</v>
+      </c>
+      <c r="L133" t="n">
+        <v>118</v>
+      </c>
+      <c r="M133" t="n">
+        <v>1.364</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:24.060</t>
+          <t>2026-05-29 09:49:36.659</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>1779509360071</v>
+        <v>1780022975869</v>
       </c>
       <c r="C134" t="n">
-        <v>90675</v>
+        <v>74979</v>
       </c>
       <c r="D134" t="n">
-        <v>3140.57</v>
+        <v>156.68</v>
       </c>
       <c r="E134" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="F134" t="n">
-        <v>1027</v>
+        <v>679</v>
       </c>
       <c r="G134" t="n">
-        <v>205.12</v>
+        <v>225.49</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I134" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J134" t="n">
+        <v>35</v>
+      </c>
+      <c r="K134" t="n">
+        <v>788</v>
+      </c>
+      <c r="L134" t="n">
+        <v>92</v>
+      </c>
+      <c r="M134" t="n">
+        <v>1.083</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:24.810</t>
+          <t>2026-05-29 09:49:37.049</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>1779509360273</v>
+        <v>1780022976088</v>
       </c>
       <c r="C135" t="n">
-        <v>90887</v>
+        <v>75044</v>
       </c>
       <c r="D135" t="n">
-        <v>3195.54</v>
+        <v>213.85</v>
       </c>
       <c r="E135" t="n">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="F135" t="n">
-        <v>1027</v>
+        <v>660</v>
       </c>
       <c r="G135" t="n">
-        <v>205.12</v>
+        <v>224.23</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I135" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J135" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K135" t="n">
+        <v>961</v>
+      </c>
+      <c r="L135" t="n">
+        <v>113</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.45</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:25.086</t>
+          <t>2026-05-29 09:49:37.425</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>1779509360474</v>
+        <v>1780022976288</v>
       </c>
       <c r="C136" t="n">
-        <v>90997</v>
+        <v>74832</v>
       </c>
       <c r="D136" t="n">
-        <v>3145.77</v>
+        <v>-8.85</v>
       </c>
       <c r="E136" t="n">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="F136" t="n">
-        <v>1027</v>
+        <v>660</v>
       </c>
       <c r="G136" t="n">
-        <v>205.12</v>
+        <v>224.23</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I136" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="J136" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="K136" t="n">
+        <v>1137</v>
+      </c>
+      <c r="L136" t="n">
+        <v>110</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.672</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:25.087</t>
+          <t>2026-05-29 09:49:37.427</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>1779509360675</v>
+        <v>1780022976488</v>
       </c>
       <c r="C137" t="n">
-        <v>90997</v>
+        <v>75123</v>
       </c>
       <c r="D137" t="n">
-        <v>2988.48</v>
+        <v>282.6</v>
       </c>
       <c r="E137" t="n">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="F137" t="n">
-        <v>1027</v>
+        <v>660</v>
       </c>
       <c r="G137" t="n">
-        <v>205.12</v>
+        <v>224.23</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I137" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J137" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="K137" t="n">
+        <v>938</v>
+      </c>
+      <c r="L137" t="n">
+        <v>115</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.949</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:25.092</t>
+          <t>2026-05-29 09:49:37.428</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>1779509360877</v>
+        <v>1780022976688</v>
       </c>
       <c r="C138" t="n">
-        <v>90712</v>
+        <v>75968</v>
       </c>
       <c r="D138" t="n">
-        <v>2554.05</v>
+        <v>1113.47</v>
       </c>
       <c r="E138" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="F138" t="n">
-        <v>1027</v>
+        <v>599</v>
       </c>
       <c r="G138" t="n">
-        <v>205.12</v>
+        <v>221.74</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I138" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J138" t="n">
+        <v>35</v>
+      </c>
+      <c r="K138" t="n">
+        <v>739</v>
+      </c>
+      <c r="L138" t="n">
+        <v>106</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.9419999999999999</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:25.444</t>
+          <t>2026-05-29 09:49:37.954</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1779509361078</v>
+        <v>1780022976888</v>
       </c>
       <c r="C139" t="n">
-        <v>90563</v>
+        <v>75138</v>
       </c>
       <c r="D139" t="n">
-        <v>2277.35</v>
+        <v>227.79</v>
       </c>
       <c r="E139" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="F139" t="n">
-        <v>1027</v>
+        <v>599</v>
       </c>
       <c r="G139" t="n">
-        <v>205.12</v>
+        <v>221.74</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I139" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J139" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K139" t="n">
+        <v>1065</v>
+      </c>
+      <c r="L139" t="n">
+        <v>105</v>
+      </c>
+      <c r="M139" t="n">
+        <v>1.094</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:25.716</t>
+          <t>2026-05-29 09:49:37.963</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1779509361279</v>
+        <v>1780022977088</v>
       </c>
       <c r="C140" t="n">
-        <v>90804</v>
+        <v>75253</v>
       </c>
       <c r="D140" t="n">
-        <v>2404.48</v>
+        <v>331.4</v>
       </c>
       <c r="E140" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="F140" t="n">
-        <v>1027</v>
+        <v>599</v>
       </c>
       <c r="G140" t="n">
-        <v>205.12</v>
+        <v>221.74</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I140" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J140" t="n">
+        <v>35</v>
+      </c>
+      <c r="K140" t="n">
+        <v>873</v>
+      </c>
+      <c r="L140" t="n">
+        <v>106</v>
+      </c>
+      <c r="M140" t="n">
+        <v>1.389</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:25.717</t>
+          <t>2026-05-29 09:49:38.258</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1779509361481</v>
+        <v>1780022977288</v>
       </c>
       <c r="C141" t="n">
-        <v>90572</v>
+        <v>75200</v>
       </c>
       <c r="D141" t="n">
-        <v>2052.26</v>
+        <v>261.83</v>
       </c>
       <c r="E141" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="F141" t="n">
-        <v>1027</v>
+        <v>599</v>
       </c>
       <c r="G141" t="n">
-        <v>205.12</v>
+        <v>221.74</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I141" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J141" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K141" t="n">
+        <v>969</v>
+      </c>
+      <c r="L141" t="n">
+        <v>111</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.572</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:26.148</t>
+          <t>2026-05-29 09:49:38.259</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>1779509361682</v>
+        <v>1780022977488</v>
       </c>
       <c r="C142" t="n">
-        <v>90229</v>
+        <v>75537</v>
       </c>
       <c r="D142" t="n">
-        <v>1606.65</v>
+        <v>585.74</v>
       </c>
       <c r="E142" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="F142" t="n">
-        <v>1027</v>
+        <v>900</v>
       </c>
       <c r="G142" t="n">
-        <v>205.12</v>
+        <v>229.83</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I142" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J142" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K142" t="n">
+        <v>771</v>
+      </c>
+      <c r="L142" t="n">
+        <v>105</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.5610000000000001</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:26.392</t>
+          <t>2026-05-29 09:49:38.708</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>1779509361884</v>
+        <v>1780022977707</v>
       </c>
       <c r="C143" t="n">
-        <v>90086</v>
+        <v>75251</v>
       </c>
       <c r="D143" t="n">
-        <v>1383.31</v>
+        <v>270.45</v>
       </c>
       <c r="E143" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="F143" t="n">
-        <v>1027</v>
+        <v>900</v>
       </c>
       <c r="G143" t="n">
-        <v>205.12</v>
+        <v>229.83</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I143" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J143" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K143" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L143" t="n">
+        <v>108</v>
+      </c>
+      <c r="M143" t="n">
+        <v>1.289</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:26.403</t>
+          <t>2026-05-29 09:49:38.709</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>1779509362085</v>
+        <v>1780022977907</v>
       </c>
       <c r="C144" t="n">
-        <v>90396</v>
+        <v>75441</v>
       </c>
       <c r="D144" t="n">
-        <v>1624.15</v>
+        <v>446.93</v>
       </c>
       <c r="E144" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="F144" t="n">
-        <v>1027</v>
+        <v>900</v>
       </c>
       <c r="G144" t="n">
-        <v>205.12</v>
+        <v>229.83</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I144" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J144" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K144" t="n">
+        <v>801</v>
+      </c>
+      <c r="L144" t="n">
+        <v>108</v>
+      </c>
+      <c r="M144" t="n">
+        <v>1.108</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:26.404</t>
+          <t>2026-05-29 09:49:39.146</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>1779509362286</v>
+        <v>1780022978107</v>
       </c>
       <c r="C145" t="n">
-        <v>90184</v>
+        <v>75207</v>
       </c>
       <c r="D145" t="n">
-        <v>1330.94</v>
+        <v>190.58</v>
       </c>
       <c r="E145" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="F145" t="n">
-        <v>4833</v>
+        <v>619</v>
       </c>
       <c r="G145" t="n">
-        <v>205.12</v>
+        <v>232.04</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I145" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J145" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K145" t="n">
+        <v>1038</v>
+      </c>
+      <c r="L145" t="n">
+        <v>110</v>
+      </c>
+      <c r="M145" t="n">
+        <v>0.578</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:26.911</t>
+          <t>2026-05-29 09:49:39.153</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>1779509362488</v>
+        <v>1780022978307</v>
       </c>
       <c r="C146" t="n">
-        <v>90268</v>
+        <v>75950</v>
       </c>
       <c r="D146" t="n">
-        <v>1348.39</v>
+        <v>924.0599999999999</v>
       </c>
       <c r="E146" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="F146" t="n">
-        <v>4833</v>
+        <v>619</v>
       </c>
       <c r="G146" t="n">
-        <v>205.12</v>
+        <v>232.04</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I146" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J146" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K146" t="n">
+        <v>845</v>
+      </c>
+      <c r="L146" t="n">
+        <v>108</v>
+      </c>
+      <c r="M146" t="n">
+        <v>0.864</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:26.912</t>
+          <t>2026-05-29 09:49:39.770</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>1779509362689</v>
+        <v>1780022978507</v>
       </c>
       <c r="C147" t="n">
-        <v>90262</v>
+        <v>75910</v>
       </c>
       <c r="D147" t="n">
-        <v>1274.97</v>
+        <v>837.85</v>
       </c>
       <c r="E147" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="F147" t="n">
-        <v>4833</v>
+        <v>619</v>
       </c>
       <c r="G147" t="n">
-        <v>205.12</v>
+        <v>232.04</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I147" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J147" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K147" t="n">
+        <v>1262</v>
+      </c>
+      <c r="L147" t="n">
+        <v>107</v>
+      </c>
+      <c r="M147" t="n">
+        <v>1.226</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:27.180</t>
+          <t>2026-05-29 09:49:39.771</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>1779509362890</v>
+        <v>1780022978707</v>
       </c>
       <c r="C148" t="n">
-        <v>90595</v>
+        <v>76118</v>
       </c>
       <c r="D148" t="n">
-        <v>1544.23</v>
+        <v>1003.96</v>
       </c>
       <c r="E148" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F148" t="n">
-        <v>563</v>
+        <v>619</v>
       </c>
       <c r="G148" t="n">
-        <v>211.59</v>
+        <v>232.04</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I148" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J148" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K148" t="n">
+        <v>1063</v>
+      </c>
+      <c r="L148" t="n">
+        <v>107</v>
+      </c>
+      <c r="M148" t="n">
+        <v>0.902</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:27.215</t>
+          <t>2026-05-29 09:49:39.773</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>1779509363092</v>
+        <v>1780022978907</v>
       </c>
       <c r="C149" t="n">
-        <v>90504</v>
+        <v>75932</v>
       </c>
       <c r="D149" t="n">
-        <v>1376.01</v>
+        <v>767.76</v>
       </c>
       <c r="E149" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F149" t="n">
-        <v>563</v>
+        <v>619</v>
       </c>
       <c r="G149" t="n">
-        <v>211.59</v>
+        <v>232.04</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I149" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J149" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K149" t="n">
+        <v>865</v>
+      </c>
+      <c r="L149" t="n">
+        <v>106</v>
+      </c>
+      <c r="M149" t="n">
+        <v>1.099</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:27.910</t>
+          <t>2026-05-29 09:49:40.134</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>1779509363293</v>
+        <v>1780022979126</v>
       </c>
       <c r="C150" t="n">
-        <v>90461</v>
+        <v>76261</v>
       </c>
       <c r="D150" t="n">
-        <v>1264.21</v>
+        <v>1058.37</v>
       </c>
       <c r="E150" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F150" t="n">
-        <v>563</v>
+        <v>619</v>
       </c>
       <c r="G150" t="n">
-        <v>211.59</v>
+        <v>232.04</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I150" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J150" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K150" t="n">
+        <v>1007</v>
+      </c>
+      <c r="L150" t="n">
+        <v>105</v>
+      </c>
+      <c r="M150" t="n">
+        <v>0.736</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-05-23 11:09:28.161</t>
+          <t>2026-05-29 09:49:40.134</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>1779509363495</v>
+        <v>1780022979326</v>
       </c>
       <c r="C151" t="n">
-        <v>90402</v>
+        <v>76652</v>
       </c>
       <c r="D151" t="n">
-        <v>1142</v>
+        <v>1396.46</v>
       </c>
       <c r="E151" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F151" t="n">
-        <v>563</v>
+        <v>619</v>
       </c>
       <c r="G151" t="n">
-        <v>211.59</v>
+        <v>232.04</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I151" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J151" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K151" t="n">
+        <v>808</v>
+      </c>
+      <c r="L151" t="n">
+        <v>105</v>
+      </c>
+      <c r="M151" t="n">
+        <v>0.473</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:49:40.467</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>1780022979526</v>
+      </c>
+      <c r="C152" t="n">
+        <v>76335</v>
+      </c>
+      <c r="D152" t="n">
+        <v>1009.63</v>
+      </c>
+      <c r="E152" t="n">
+        <v>88</v>
+      </c>
+      <c r="F152" t="n">
+        <v>619</v>
+      </c>
+      <c r="G152" t="n">
+        <v>232.04</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J152" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K152" t="n">
+        <v>939</v>
+      </c>
+      <c r="L152" t="n">
+        <v>106</v>
+      </c>
+      <c r="M152" t="n">
+        <v>1.992</v>
       </c>
     </row>
   </sheetData>
